--- a/reports/upwork-bid-funnel-aug-oct-2026.xlsx
+++ b/reports/upwork-bid-funnel-aug-oct-2026.xlsx
@@ -14,7 +14,8 @@
     <sheet name="Monthly Trend" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="By Profile" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Weekly Trend" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Notes" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Wins by Close Date" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Notes" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -85,7 +86,19 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Blank = stage never set in Notion. Only 9 of 24 interviews have a stage.</t>
+          <t xml:space="preserve">Blank = stage never set in Notion. 14 of 25 interviews have no stage.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H11" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Interview record was created on 20 Oct when the bid was back-filled, so Notion shows 20 Oct. Real date unknown; left blank here.</t>
         </r>
       </text>
     </comment>
@@ -133,6 +146,30 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
+    <comment ref="B21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Every Nstya bid in the period is an interview (checked in Notion), so the Interviews tab holds all of them.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B22" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Every INVITE bid in the period is an interview (checked in Notion), so the Interviews tab holds all of them.</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D9" authorId="0">
       <text>
         <r>
@@ -161,8 +198,30 @@
 </comments>
 </file>
 
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A9" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">John Brown is Won in Notion but has no Date Won. Add it in Upwork Bids to place this win.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="246">
   <si>
     <t xml:space="preserve">Upwork bid funnel, 1 Aug – 20 Oct 2026</t>
   </si>
@@ -200,31 +259,37 @@
     <t xml:space="preserve">Won</t>
   </si>
   <si>
-    <t xml:space="preserve">One win since 1 Aug (Selva Ganesan, Polina). It is marked Won only in Interviews, not in Upwork Bids.</t>
+    <t xml:space="preserve">3 wins from bids sent since 1 Aug: Selva Ganesan and Miss Money Savvy (Polina), Marc Staal (Shevk). 4 contracts closed in the period (see Wins by Close Date).</t>
   </si>
   <si>
     <t xml:space="preserve">Bid → Interview</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0%, flat every month (5.3%, 5.0%, 4.5%). That matches Mar–Jul (5.3%). The Jan–Jul average is lifted by Jan–Feb (10–14%).</t>
+    <t xml:space="preserve">5.2%, flat every month (5.3%, 5.6%, 4.5%). That matches Mar–Jul (5.3%). The Jan–Jul average is lifted by Jan–Feb (10–14%).</t>
   </si>
   <si>
     <t xml:space="preserve">Bid → Won</t>
   </si>
   <si>
-    <t xml:space="preserve">The real drop. Jan–Jul turned about 1 in 84 bids into a win; Aug–Oct is 1 in 481.</t>
+    <t xml:space="preserve">Down from 1.2% (1 in 84 bids) to 0.6% (1 in 161). Mar–Jul was 1.0%.</t>
   </si>
   <si>
     <t xml:space="preserve">Interview → Won</t>
   </si>
   <si>
-    <t xml:space="preserve">Interviews are not closing: 1 of 24 vs 25 of 158 (16%). 15 of 24 have no stage set and none has a Lost reason.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organic Bid → Interview (Leadgen = Alex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strips out 5 Nstya / INVITE bids that are logged only after they convert.</t>
+    <t xml:space="preserve">3 of 25 (12%) vs 16% in Jan–Jul and 19% in Mar–Jul. 14 of 25 interviews have no stage and none has a Lost reason.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Organic Bid → Interview (Alex + Nstya)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excludes 1 INVITE (client invitation).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contracts closed in Aug–Oct (by Date Won)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Jacoby, Selva Ganesan, Miss Money Savvy, Marc Staal. 3 of the 4 came through Nstya.</t>
   </si>
   <si>
     <t xml:space="preserve">Avg days from bid to interview</t>
@@ -251,22 +316,25 @@
     <t xml:space="preserve">Findings</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Yulia carries the funnel. She sends 60% of bids (288) and gets 19 of 24 interviews: 6.6% overall, 5.6% organic. That's down from 8.2% in Jan–Jul but still the best profile.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Polina sends 22% of bids (104) at 2.9% (1.9% organic, 2 of 103), down from 7.1%. Her one Won (Selva Ganesan) is a test assignment the client didn't continue, per the Upwork thread.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Andrew (41 bids, 1 interview, 2.4%) and Shevk (48 bids, 0 organic interviews) are the weakest. In Jan–Jul they ran at 8.6% and 5.3%. Shevk's only interview (Marc Staal) came through Nstya.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Full weeks hold at 34–51 bids. Interviews come in bursts: 4 in the week of 17 Aug and 5 in the week of 28 Sep, none in the weeks of 24 Aug and 5 Oct. The rolling 4-week rate sits between 3% and 7%.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. Bid → Interview is in line with Mar–Jul (5.0% vs 5.3%). The drop is after the interview: Interview → Won fell from 19% in Mar–Jul (14 of 74) to 4% (1 of 24).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. Data gaps limit the win analysis. No bid since 1 Aug has Status = Won, 15 of 24 interviews have no Interview Stage and none has a Lost reason. 8 interviews are still open (Waiting / Estimation) and may still close.</t>
+    <t xml:space="preserve">1. Yulia carries the bid volume. She sends 60% of bids (288) and gets 19 of 25 interviews (6.6%, 6.3% organic), the best interview rate of any profile. That's down from 8.2% in Jan–Jul, and none of her Aug–Oct bids has closed yet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Polina converts best to contracts. 105 bids, 4 interviews (3.8%), 2 wins (Selva Ganesan and Miss Money Savvy): 1.9% Bid → Won and 50% Interview → Won.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Shevk (48 bids) and Andrew (41 bids) get 1 interview each. Shevk's one interview, Marc Staal, came through Nstya and closed (2.1% Bid → Won on one deal). Andrew's Jan–Jul rate was 8.6%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Nstya's leads close. All 5 of her bids since 1 Aug became interviews and 2 closed. She also sourced 3 of the 4 contracts that closed in Aug–Oct, plus John Brown. Alex's 476 bids gave 19 interviews (4.0%) and 1 win.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Bid → Interview matches Mar–Jul (5.2% vs 5.3%). The drop is after the interview: Interview → Won is 12% vs 19% in Mar–Jul, and Alex-sourced interviews closed 1 of 19.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. Full weeks hold at 34–51 bids. Interviews come in bursts: 4 in the week of 17 Aug, 5 in the week of 28 Sep, none in the weeks of 24 Aug and 5 Oct.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. Data gaps. 14 of 25 interviews have no Interview Stage and none has a Lost reason. 8 are still open (Waiting / Estimation). John Brown has no Date Won.</t>
   </si>
   <si>
     <t xml:space="preserve">Bid Date</t>
@@ -305,6 +373,9 @@
     <t xml:space="preserve">Interview page</t>
   </si>
   <si>
+    <t xml:space="preserve">Date Won</t>
+  </si>
+  <si>
     <t xml:space="preserve">Yulia</t>
   </si>
   <si>
@@ -434,6 +505,21 @@
     <t xml:space="preserve">Polina</t>
   </si>
   <si>
+    <t xml:space="preserve">Miss Money Savvy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WordPress Designer &amp; Developer – UK Consumer Brand Website Redesign &amp; Rebuild</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interview, Won</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://app.notion.com/p/3ffbd8b60a638145bda3f714ba95b244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://app.notion.com/p/3ffbd8b60a6381b08276f6ac45a7b9f9</t>
+  </si>
+  <si>
     <t xml:space="preserve">Selva Ganesan</t>
   </si>
   <si>
@@ -593,21 +679,21 @@
     <t xml:space="preserve">Wordpress developer for a start-up</t>
   </si>
   <si>
+    <t xml:space="preserve">https://app.notion.com/p/3f7bd8b60a638005ac71ff3702d1cc69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://app.notion.com/p/3f7bd8b60a6381a98a0beffc50495ba7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anish Bhalsod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI/UX + Graphic Designer</t>
+  </si>
+  <si>
     <t xml:space="preserve">Estimation</t>
   </si>
   <si>
-    <t xml:space="preserve">https://app.notion.com/p/3f7bd8b60a638005ac71ff3702d1cc69</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://app.notion.com/p/3f7bd8b60a6381a98a0beffc50495ba7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anish Bhalsod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UI/UX + Graphic Designer</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://app.notion.com/p/3fbbd8b60a6380cfa966da65cf868718</t>
   </si>
   <si>
@@ -707,13 +793,13 @@
     <t xml:space="preserve">Upwork profile performance, 1 Aug – 20 Oct 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">"Organic" = bids where Leadgen = Alex. Nstya / INVITE bids are only logged once they convert, which inflates the all-bids rate.</t>
+    <t xml:space="preserve">"Organic" = Leadgen Alex or Nstya. INVITE (client invitations) is excluded because we did not bid cold.</t>
   </si>
   <si>
     <t xml:space="preserve">Share of bids</t>
   </si>
   <si>
-    <t xml:space="preserve">Organic bids (Leadgen = Alex)</t>
+    <t xml:space="preserve">Organic bids (Alex + Nstya)</t>
   </si>
   <si>
     <t xml:space="preserve">Organic interviews</t>
@@ -737,7 +823,7 @@
     <t xml:space="preserve">Check: interviews in Interviews tab</t>
   </si>
   <si>
-    <t xml:space="preserve">Check: non-organic bids (Nstya / INVITE) = their interviews, i.e. logged only on conversion</t>
+    <t xml:space="preserve">Check: INVITE bids in period (all are interviews, per Notion query)</t>
   </si>
   <si>
     <t xml:space="preserve">bids</t>
@@ -746,7 +832,13 @@
     <t xml:space="preserve">Best Bid → Won</t>
   </si>
   <si>
-    <t xml:space="preserve">1 win in the period; too few to rank profiles on wins</t>
+    <t xml:space="preserve">3 wins in the cohort (Polina 2, Shevk 1); too few to rank reliably</t>
+  </si>
+  <si>
+    <t xml:space="preserve">By Leadgen (Aug–Oct bids)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All 5 Nstya bids since 1 Aug became interviews, so her Bid → Interview reads 100%.</t>
   </si>
   <si>
     <t xml:space="preserve">Weekly funnel (weeks start Monday; first week counts 1–2 Aug only, last week counts 19–20 Oct)</t>
@@ -785,6 +877,39 @@
     <t xml:space="preserve">Source: Notion Upwork Bids grouped by week of Bid Date and Upwork Profile, pulled 2026-10-20 (blue). Interviews / Won count live from the Interviews tab.</t>
   </si>
   <si>
+    <t xml:space="preserve">Contracts won by the date they closed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Includes wins from bids sent before 1 Aug. Source: Notion Upwork Bids + Interviews after the 20 Oct fixes (blue).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days bid → won</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Closed in Aug–Oct (1/0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Jacoby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WordPress/ WooCommerce- ACF master</t>
+  </si>
+  <si>
+    <t xml:space="preserve">John Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WordPress Designer/Developer for Flight School Website</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Closed Aug–Oct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…of which Leadgen Nstya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avg days bid → won</t>
+  </si>
+  <si>
     <t xml:space="preserve">Definitions</t>
   </si>
   <si>
@@ -794,37 +919,40 @@
     <t xml:space="preserve">Bid → Won = won ÷ bids. Interview → Won = won ÷ interviews.</t>
   </si>
   <si>
-    <t xml:space="preserve">Interview = Upwork Bids Status contains "Interview". All 24 since 1 Aug have a matching Interviews record.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Won (Aug–Oct) = Bids Status contains "Won" OR Interviews Stage = "Won". Won (Jan–Jul) = Bids Status only. This may understate baseline wins a little.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organic = Leadgen "Alex". Leadgen "Nstya" (4 bids) and "INVITE" (1 bid) appear only once they converted, so they show a false 100% rate.</t>
+    <t xml:space="preserve">Interview = Upwork Bids Status contains "Interview". All 25 since 1 Aug have a matching Interviews record.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Won = Bids Status contains "Won" OR Interviews Stage = "Won". Statuses were corrected in Notion on 20 Oct (Selva Ganesan, Marc Staal, Miss Money Savvy). Jan–Jul wins come from Bids Status only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Organic = Leadgen Alex or Nstya. INVITE (1 bid, a client invitation) is excluded. All 5 Nstya bids since 1 Aug are interviews.</t>
   </si>
   <si>
     <t xml:space="preserve">Recent wins outside the cohort (bid sent before 1 Aug)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ben Jacoby (Yulia, bid 24 Jul, won 5 Aug) and John Brown (Yulia, bid 8 Jul, Stage Won). Counted in July, not in Aug–Oct.</t>
+    <t xml:space="preserve">Ben Jacoby (Yulia / Nstya, bid 24 Jul, won 5 Aug) and John Brown (Yulia / Nstya, bid 8 Jul, no Date Won). Their bids count in July. The Wins by Close Date tab shows them by close date.</t>
   </si>
   <si>
     <t xml:space="preserve">Data issues to fix in Notion</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Selva Ganesan is Won in Interviews but not in Upwork Bids Status.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. 15 of 24 interviews have no Interview Stage. None has a Lost reason.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. "Kevin Marcum" interview page is titled with the job name.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Interview Started for Michael Wong (9 Oct) is 53 days after the bid. The Interviews record was probably created late.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. Bids from Leadgen Nstya are logged only when they convert. To compare leadgens, log all Nstya bids.</t>
+    <t xml:space="preserve">1. Fixed 20 Oct: Selva Ganesan and Marc Staal set to Won with Date Won. Ben Jacoby Date Won corrected to 5 Aug. John Brown Leadgen set to Nstya. Miss Money Savvy bid and Interview added (bid date 3 Sep assumed from the job page).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Miss Money Savvy Interview Started reads 20 Oct (record created then). Set the real date.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. 14 of 25 interviews have no Interview Stage. None has a Lost reason.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. John Brown has no Date Won.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. A duplicate "WordPress/ WooCommerce- ACF master" bid row (24 Jul, no status) is still in Upwork Bids. It counts as one extra July bid.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. "Kevin Marcum" interview page is titled with the job name.</t>
   </si>
   <si>
     <t xml:space="preserve">Colour key: blue text = values copied from Notion (edit these to update), black = formulas.</t>
@@ -1018,7 +1146,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1121,6 +1249,10 @@
     </xf>
     <xf numFmtId="174" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -1369,7 +1501,7 @@
                   <c:v>0.0529411764705882</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.0502793296089386</c:v>
+                  <c:v>0.0555555555555556</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0.0454545454545455</c:v>
@@ -1387,11 +1519,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="24711966"/>
-        <c:axId val="62064957"/>
+        <c:axId val="80789918"/>
+        <c:axId val="93845232"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="24711966"/>
+        <c:axId val="80789918"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1423,7 +1555,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="62064957"/>
+        <c:crossAx val="93845232"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1431,7 +1563,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="62064957"/>
+        <c:axId val="93845232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1507,7 +1639,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24711966"/>
+        <c:crossAx val="80789918"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1721,7 +1853,7 @@
                   <c:v>170</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>179</c:v>
+                  <c:v>180</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>132</c:v>
@@ -1732,11 +1864,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="41509499"/>
-        <c:axId val="64805181"/>
+        <c:axId val="34450838"/>
+        <c:axId val="6714831"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="41509499"/>
+        <c:axId val="34450838"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1768,7 +1900,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64805181"/>
+        <c:crossAx val="6714831"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1776,7 +1908,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="64805181"/>
+        <c:axId val="6714831"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1818,7 +1950,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="41509499"/>
+        <c:crossAx val="34450838"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1993,7 +2125,7 @@
                   <c:v>288</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>104</c:v>
+                  <c:v>105</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>48</c:v>
@@ -2007,11 +2139,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="39156027"/>
-        <c:axId val="82967012"/>
+        <c:axId val="40821025"/>
+        <c:axId val="65947225"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="39156027"/>
+        <c:axId val="40821025"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2043,7 +2175,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="82967012"/>
+        <c:crossAx val="65947225"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2051,7 +2183,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="82967012"/>
+        <c:axId val="65947225"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2093,7 +2225,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39156027"/>
+        <c:crossAx val="40821025"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2268,7 +2400,7 @@
                   <c:v>0.0659722222222222</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.0288461538461538</c:v>
+                  <c:v>0.0380952380952381</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0.0208333333333333</c:v>
@@ -2355,13 +2487,13 @@
                 <c:formatCode>0.0%;\-0.0%;\-</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.056140350877193</c:v>
+                  <c:v>0.0627177700348432</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.0194174757281553</c:v>
+                  <c:v>0.0380952380952381</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.0208333333333333</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0.024390243902439</c:v>
@@ -2462,11 +2594,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="35607884"/>
-        <c:axId val="35759569"/>
+        <c:axId val="4502693"/>
+        <c:axId val="65992635"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="35607884"/>
+        <c:axId val="4502693"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2498,7 +2630,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="35759569"/>
+        <c:crossAx val="65992635"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2506,7 +2638,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="35759569"/>
+        <c:axId val="65992635"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2548,7 +2680,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="35607884"/>
+        <c:crossAx val="4502693"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2906,7 +3038,7 @@
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>12</c:v>
@@ -3223,8 +3355,8 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="16136535"/>
-        <c:axId val="81864002"/>
+        <c:axId val="83480587"/>
+        <c:axId val="39626519"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="stacked"/>
@@ -3342,16 +3474,16 @@
                   <c:v>0.0529801324503311</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.0454545454545455</c:v>
+                  <c:v>0.0516129032258065</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.0454545454545455</c:v>
+                  <c:v>0.0516129032258065</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.0304878048780488</c:v>
+                  <c:v>0.0363636363636364</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.0421686746987952</c:v>
+                  <c:v>0.0479041916167665</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0.0561797752808989</c:v>
@@ -3378,11 +3510,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="24745148"/>
-        <c:axId val="12190016"/>
+        <c:axId val="12087743"/>
+        <c:axId val="29905977"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="16136535"/>
+        <c:axId val="83480587"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3414,7 +3546,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81864002"/>
+        <c:crossAx val="39626519"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3422,7 +3554,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="81864002"/>
+        <c:axId val="39626519"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3464,12 +3596,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16136535"/>
+        <c:crossAx val="83480587"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="24745148"/>
+        <c:axId val="12087743"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3501,7 +3633,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="12190016"/>
+        <c:crossAx val="29905977"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3509,7 +3641,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="12190016"/>
+        <c:axId val="29905977"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3575,7 +3707,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24745148"/>
+        <c:crossAx val="12087743"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3698,14 +3830,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>160560</xdr:rowOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>39240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>528480</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>2880</xdr:rowOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>72000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3713,7 +3845,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="3638520"/>
+        <a:off x="0" y="4971960"/>
         <a:ext cx="5039640" cy="2699640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -3728,14 +3860,14 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>160560</xdr:rowOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>39240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>2880</xdr:rowOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>72000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -3743,7 +3875,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="5286240" y="3638520"/>
+        <a:off x="5286240" y="4971960"/>
         <a:ext cx="5759640" cy="2699640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -3972,7 +4104,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
@@ -4028,7 +4160,7 @@
       </c>
       <c r="B5" s="6" t="n">
         <f aca="false">'Monthly Trend'!C17</f>
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C5" s="6" t="n">
         <f aca="false">'Monthly Trend'!C16</f>
@@ -4036,7 +4168,7 @@
       </c>
       <c r="D5" s="7" t="n">
         <f aca="false">IFERROR((B5/'Monthly Trend'!I17)/(C5/'Monthly Trend'!I16)-1,0)</f>
-        <v>-0.401087735372544</v>
+        <v>-0.399842595529243</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>8</v>
@@ -4048,7 +4180,7 @@
       </c>
       <c r="B6" s="9" t="n">
         <f aca="false">'Monthly Trend'!J17</f>
-        <v>5.93827160493827</v>
+        <v>5.95061728395062</v>
       </c>
       <c r="C6" s="9" t="n">
         <f aca="false">'Monthly Trend'!J16</f>
@@ -4056,7 +4188,7 @@
       </c>
       <c r="D6" s="10" t="n">
         <f aca="false">B6-C6</f>
-        <v>-3.97682273468437</v>
+        <v>-3.96447705567202</v>
       </c>
       <c r="E6" s="8"/>
     </row>
@@ -4066,7 +4198,7 @@
       </c>
       <c r="B7" s="6" t="n">
         <f aca="false">'Monthly Trend'!D17</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" s="6" t="n">
         <f aca="false">'Monthly Trend'!D16</f>
@@ -4074,17 +4206,17 @@
       </c>
       <c r="D7" s="7" t="n">
         <f aca="false">IFERROR((B7/'Monthly Trend'!I17)/(C7/'Monthly Trend'!I16)-1,0)</f>
-        <v>-0.602437880918894</v>
+        <v>-0.585872792623847</v>
       </c>
       <c r="E7" s="8"/>
     </row>
-    <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="6" t="n">
         <f aca="false">'Monthly Trend'!E17</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C8" s="6" t="n">
         <f aca="false">'Monthly Trend'!E16</f>
@@ -4092,7 +4224,7 @@
       </c>
       <c r="D8" s="7" t="n">
         <f aca="false">IFERROR((B8/'Monthly Trend'!I17)/(C8/'Monthly Trend'!I16)-1,0)</f>
-        <v>-0.895308641975309</v>
+        <v>-0.685925925925926</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>12</v>
@@ -4104,7 +4236,7 @@
       </c>
       <c r="B9" s="11" t="n">
         <f aca="false">'Monthly Trend'!F17</f>
-        <v>0.0498960498960499</v>
+        <v>0.0518672199170125</v>
       </c>
       <c r="C9" s="11" t="n">
         <f aca="false">'Monthly Trend'!F16</f>
@@ -4112,19 +4244,19 @@
       </c>
       <c r="D9" s="12" t="n">
         <f aca="false">B9-C9</f>
-        <v>-0.0252704581914858</v>
+        <v>-0.0232992881705232</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B10" s="11" t="n">
         <f aca="false">'Monthly Trend'!G17</f>
-        <v>0.00207900207900208</v>
+        <v>0.00622406639004149</v>
       </c>
       <c r="C10" s="11" t="n">
         <f aca="false">'Monthly Trend'!G16</f>
@@ -4132,7 +4264,7 @@
       </c>
       <c r="D10" s="12" t="n">
         <f aca="false">B10-C10</f>
-        <v>-0.00981443274497509</v>
+        <v>-0.00566936843393567</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>16</v>
@@ -4144,7 +4276,7 @@
       </c>
       <c r="B11" s="11" t="n">
         <f aca="false">'Monthly Trend'!H17</f>
-        <v>0.0416666666666667</v>
+        <v>0.12</v>
       </c>
       <c r="C11" s="11" t="n">
         <f aca="false">'Monthly Trend'!H16</f>
@@ -4152,7 +4284,7 @@
       </c>
       <c r="D11" s="12" t="n">
         <f aca="false">B11-C11</f>
-        <v>-0.116561181434599</v>
+        <v>-0.0382278481012658</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>18</v>
@@ -4164,7 +4296,7 @@
       </c>
       <c r="B12" s="11" t="n">
         <f aca="false">'By Profile'!K9</f>
-        <v>0.0399159663865546</v>
+        <v>0.0498960498960499</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="2"/>
@@ -4172,204 +4304,209 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="9" t="n">
-        <f aca="false">Interviews!J26</f>
+      <c r="B13" s="6" t="n">
+        <f aca="false">'Wins by Close Date'!H11</f>
+        <v>4</v>
+      </c>
+      <c r="C13" s="6"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="9" t="n">
+        <f aca="false">Interviews!J27</f>
         <v>4.25</v>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="8"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
+      <c r="C14" s="9"/>
       <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
+      <c r="E14" s="8"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
-        <v>22</v>
-      </c>
+      <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="4" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="4" t="s">
+      <c r="D17" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="str">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="str">
         <f aca="false">'By Profile'!A5</f>
         <v>Yulia</v>
       </c>
-      <c r="B17" s="2" t="n">
+      <c r="B18" s="2" t="n">
         <f aca="false">'By Profile'!B5</f>
         <v>288</v>
       </c>
-      <c r="C17" s="11" t="n">
+      <c r="C18" s="11" t="n">
         <f aca="false">'By Profile'!F5</f>
         <v>0.0659722222222222</v>
       </c>
-      <c r="D17" s="11" t="n">
+      <c r="D18" s="11" t="n">
         <f aca="false">'By Profile'!K5</f>
-        <v>0.056140350877193</v>
-      </c>
-      <c r="E17" s="2" t="n">
+        <v>0.0627177700348432</v>
+      </c>
+      <c r="E18" s="2" t="n">
         <f aca="false">'By Profile'!E5</f>
         <v>0</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="str">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="str">
         <f aca="false">'By Profile'!A6</f>
         <v>Polina</v>
       </c>
-      <c r="B18" s="2" t="n">
+      <c r="B19" s="2" t="n">
         <f aca="false">'By Profile'!B6</f>
-        <v>104</v>
-      </c>
-      <c r="C18" s="11" t="n">
+        <v>105</v>
+      </c>
+      <c r="C19" s="11" t="n">
         <f aca="false">'By Profile'!F6</f>
-        <v>0.0288461538461538</v>
-      </c>
-      <c r="D18" s="11" t="n">
+        <v>0.0380952380952381</v>
+      </c>
+      <c r="D19" s="11" t="n">
         <f aca="false">'By Profile'!K6</f>
-        <v>0.0194174757281553</v>
-      </c>
-      <c r="E18" s="2" t="n">
+        <v>0.0380952380952381</v>
+      </c>
+      <c r="E19" s="2" t="n">
         <f aca="false">'By Profile'!E6</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="str">
         <f aca="false">'By Profile'!A7</f>
         <v>Shevk</v>
       </c>
-      <c r="B19" s="2" t="n">
+      <c r="B20" s="2" t="n">
         <f aca="false">'By Profile'!B7</f>
         <v>48</v>
       </c>
-      <c r="C19" s="11" t="n">
+      <c r="C20" s="11" t="n">
         <f aca="false">'By Profile'!F7</f>
         <v>0.0208333333333333</v>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="D20" s="11" t="n">
         <f aca="false">'By Profile'!K7</f>
-        <v>0</v>
-      </c>
-      <c r="E19" s="2" t="n">
+        <v>0.0208333333333333</v>
+      </c>
+      <c r="E20" s="2" t="n">
         <f aca="false">'By Profile'!E7</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="str">
         <f aca="false">'By Profile'!A8</f>
         <v>Andrew</v>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B21" s="2" t="n">
         <f aca="false">'By Profile'!B8</f>
         <v>41</v>
       </c>
-      <c r="C20" s="11" t="n">
+      <c r="C21" s="11" t="n">
         <f aca="false">'By Profile'!F8</f>
         <v>0.024390243902439</v>
       </c>
-      <c r="D20" s="11" t="n">
+      <c r="D21" s="11" t="n">
         <f aca="false">'By Profile'!K8</f>
         <v>0.024390243902439</v>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="E21" s="2" t="n">
         <f aca="false">'By Profile'!E8</f>
         <v>0</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-    </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="2" t="str">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="2" t="str">
         <f aca="false">'By Profile'!B14</f>
         <v>Yulia</v>
       </c>
-      <c r="C22" s="2" t="n">
+      <c r="C23" s="2" t="n">
         <f aca="false">'By Profile'!C14</f>
         <v>288</v>
       </c>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="2" t="str">
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="2" t="str">
         <f aca="false">'By Profile'!B15</f>
         <v>Yulia</v>
       </c>
-      <c r="C23" s="11" t="n">
+      <c r="C24" s="11" t="n">
         <f aca="false">'By Profile'!C15</f>
-        <v>0.056140350877193</v>
-      </c>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
+        <v>0.0627177700348432</v>
+      </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13" t="s">
-        <v>28</v>
-      </c>
+      <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
     </row>
-    <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B27" s="14"/>
       <c r="C27" s="14"/>
@@ -4378,7 +4515,7 @@
     </row>
     <row r="28" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
@@ -4387,7 +4524,7 @@
     </row>
     <row r="29" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
@@ -4396,7 +4533,7 @@
     </row>
     <row r="30" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B30" s="14"/>
       <c r="C30" s="14"/>
@@ -4405,21 +4542,40 @@
     </row>
     <row r="31" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B31" s="14"/>
       <c r="C31" s="14"/>
       <c r="D31" s="14"/>
       <c r="E31" s="14"/>
     </row>
+    <row r="32" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+    </row>
+    <row r="33" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="14"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A26:E26"/>
+  <mergeCells count="7">
     <mergeCell ref="A27:E27"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A33:E33"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4437,7 +4593,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -4451,44 +4607,48 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4496,19 +4656,19 @@
         <v>46235</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G2" s="16"/>
       <c r="H2" s="15" t="n">
@@ -4519,34 +4679,35 @@
         <v>0</v>
       </c>
       <c r="J2" s="17" t="n">
-        <f aca="false">H2-A2</f>
+        <f aca="false">IF(H2="","",H2-A2)</f>
         <v>12</v>
       </c>
       <c r="K2" s="18" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="L2" s="18" t="s">
-        <v>53</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="M2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="n">
         <v>46237</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D3" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="16" t="s">
         <v>55</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>51</v>
       </c>
       <c r="G3" s="16"/>
       <c r="H3" s="15" t="n">
@@ -4557,34 +4718,35 @@
         <v>0</v>
       </c>
       <c r="J3" s="17" t="n">
-        <f aca="false">H3-A3</f>
+        <f aca="false">IF(H3="","",H3-A3)</f>
         <v>0</v>
       </c>
       <c r="K3" s="18" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="L3" s="18" t="s">
-        <v>58</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="M3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="n">
         <v>46242</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G4" s="16"/>
       <c r="H4" s="15" t="n">
@@ -4595,34 +4757,35 @@
         <v>0</v>
       </c>
       <c r="J4" s="17" t="n">
-        <f aca="false">H4-A4</f>
+        <f aca="false">IF(H4="","",H4-A4)</f>
         <v>2</v>
       </c>
       <c r="K4" s="18" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="L4" s="18" t="s">
-        <v>62</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="M4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="n">
         <v>46243</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G5" s="16"/>
       <c r="H5" s="15" t="n">
@@ -4633,34 +4796,35 @@
         <v>0</v>
       </c>
       <c r="J5" s="17" t="n">
-        <f aca="false">H5-A5</f>
+        <f aca="false">IF(H5="","",H5-A5)</f>
         <v>3</v>
       </c>
       <c r="K5" s="18" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="L5" s="18" t="s">
-        <v>66</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="M5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="n">
         <v>46248</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G6" s="16"/>
       <c r="H6" s="15" t="n">
@@ -4671,34 +4835,35 @@
         <v>0</v>
       </c>
       <c r="J6" s="17" t="n">
-        <f aca="false">H6-A6</f>
+        <f aca="false">IF(H6="","",H6-A6)</f>
         <v>0</v>
       </c>
       <c r="K6" s="18" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="L6" s="18" t="s">
-        <v>70</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="M6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="n">
         <v>46251</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G7" s="16"/>
       <c r="H7" s="15" t="n">
@@ -4709,37 +4874,38 @@
         <v>0</v>
       </c>
       <c r="J7" s="17" t="n">
-        <f aca="false">H7-A7</f>
+        <f aca="false">IF(H7="","",H7-A7)</f>
         <v>1</v>
       </c>
       <c r="K7" s="18" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="L7" s="18" t="s">
-        <v>74</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="M7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="n">
         <v>46251</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>46304</v>
@@ -4749,34 +4915,35 @@
         <v>0</v>
       </c>
       <c r="J8" s="17" t="n">
-        <f aca="false">H8-A8</f>
+        <f aca="false">IF(H8="","",H8-A8)</f>
         <v>53</v>
       </c>
       <c r="K8" s="18" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="L8" s="18" t="s">
-        <v>80</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="M8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="n">
         <v>46253</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G9" s="16"/>
       <c r="H9" s="15" t="n">
@@ -4787,34 +4954,35 @@
         <v>0</v>
       </c>
       <c r="J9" s="17" t="n">
-        <f aca="false">H9-A9</f>
+        <f aca="false">IF(H9="","",H9-A9)</f>
         <v>2</v>
       </c>
       <c r="K9" s="18" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="L9" s="18" t="s">
-        <v>84</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="M9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="n">
         <v>46257</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G10" s="16"/>
       <c r="H10" s="15" t="n">
@@ -4825,150 +4993,158 @@
         <v>0</v>
       </c>
       <c r="J10" s="17" t="n">
-        <f aca="false">H10-A10</f>
+        <f aca="false">IF(H10="","",H10-A10)</f>
         <v>4</v>
       </c>
       <c r="K10" s="18" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="L10" s="18" t="s">
-        <v>88</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="M10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="n">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="G11" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="H11" s="15" t="n">
-        <v>46271</v>
-      </c>
+      <c r="H11" s="15"/>
       <c r="I11" s="17" t="n">
         <f aca="false">IF(OR(ISNUMBER(SEARCH("Won",F11)),G11="Won"),1,0)</f>
         <v>1</v>
       </c>
-      <c r="J11" s="17" t="n">
-        <f aca="false">H11-A11</f>
-        <v>2</v>
+      <c r="J11" s="17" t="str">
+        <f aca="false">IF(H11="","",H11-A11)</f>
+        <v/>
       </c>
       <c r="K11" s="18" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="L11" s="18" t="s">
-        <v>93</v>
+        <v>98</v>
+      </c>
+      <c r="M11" s="15" t="n">
+        <v>46283</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="n">
-        <v>46271</v>
+        <v>46269</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>47</v>
+        <v>93</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="G12" s="16"/>
+        <v>96</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>11</v>
+      </c>
       <c r="H12" s="15" t="n">
         <v>46271</v>
       </c>
       <c r="I12" s="17" t="n">
         <f aca="false">IF(OR(ISNUMBER(SEARCH("Won",F12)),G12="Won"),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="17" t="n">
-        <f aca="false">H12-A12</f>
-        <v>0</v>
+        <f aca="false">IF(H12="","",H12-A12)</f>
+        <v>2</v>
       </c>
       <c r="K12" s="18" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="L12" s="18" t="s">
-        <v>97</v>
+        <v>102</v>
+      </c>
+      <c r="M12" s="15" t="n">
+        <v>46273</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="n">
-        <v>46275</v>
+        <v>46271</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>89</v>
+        <v>51</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G13" s="16"/>
       <c r="H13" s="15" t="n">
-        <v>46281</v>
+        <v>46271</v>
       </c>
       <c r="I13" s="17" t="n">
         <f aca="false">IF(OR(ISNUMBER(SEARCH("Won",F13)),G13="Won"),1,0)</f>
         <v>0</v>
       </c>
       <c r="J13" s="17" t="n">
-        <f aca="false">H13-A13</f>
-        <v>6</v>
+        <f aca="false">IF(H13="","",H13-A13)</f>
+        <v>0</v>
       </c>
       <c r="K13" s="18" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="L13" s="18" t="s">
-        <v>101</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="M13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="n">
-        <v>46280</v>
+        <v>46275</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>47</v>
+        <v>93</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G14" s="16"/>
       <c r="H14" s="15" t="n">
@@ -4979,233 +5155,237 @@
         <v>0</v>
       </c>
       <c r="J14" s="17" t="n">
-        <f aca="false">H14-A14</f>
-        <v>1</v>
+        <f aca="false">IF(H14="","",H14-A14)</f>
+        <v>6</v>
       </c>
       <c r="K14" s="18" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="L14" s="18" t="s">
-        <v>105</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="M14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G15" s="16"/>
       <c r="H15" s="15" t="n">
-        <v>46283</v>
+        <v>46281</v>
       </c>
       <c r="I15" s="17" t="n">
         <f aca="false">IF(OR(ISNUMBER(SEARCH("Won",F15)),G15="Won"),1,0)</f>
         <v>0</v>
       </c>
       <c r="J15" s="17" t="n">
-        <f aca="false">H15-A15</f>
-        <v>2</v>
+        <f aca="false">IF(H15="","",H15-A15)</f>
+        <v>1</v>
       </c>
       <c r="K15" s="18" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="L15" s="18" t="s">
-        <v>109</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="M15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="n">
-        <v>46286</v>
+        <v>46281</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G16" s="16"/>
       <c r="H16" s="15" t="n">
-        <v>46287</v>
+        <v>46283</v>
       </c>
       <c r="I16" s="17" t="n">
         <f aca="false">IF(OR(ISNUMBER(SEARCH("Won",F16)),G16="Won"),1,0)</f>
         <v>0</v>
       </c>
       <c r="J16" s="17" t="n">
-        <f aca="false">H16-A16</f>
-        <v>1</v>
+        <f aca="false">IF(H16="","",H16-A16)</f>
+        <v>2</v>
       </c>
       <c r="K16" s="18" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="L16" s="18" t="s">
-        <v>113</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="M16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="n">
-        <v>46290</v>
+        <v>46286</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="G17" s="16" t="s">
-        <v>78</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="G17" s="16"/>
       <c r="H17" s="15" t="n">
-        <v>46297</v>
+        <v>46287</v>
       </c>
       <c r="I17" s="17" t="n">
         <f aca="false">IF(OR(ISNUMBER(SEARCH("Won",F17)),G17="Won"),1,0)</f>
         <v>0</v>
       </c>
       <c r="J17" s="17" t="n">
-        <f aca="false">H17-A17</f>
-        <v>7</v>
+        <f aca="false">IF(H17="","",H17-A17)</f>
+        <v>1</v>
       </c>
       <c r="K17" s="18" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="L17" s="18" t="s">
-        <v>117</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="M17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="n">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="I18" s="17" t="n">
         <f aca="false">IF(OR(ISNUMBER(SEARCH("Won",F18)),G18="Won"),1,0)</f>
         <v>0</v>
       </c>
       <c r="J18" s="17" t="n">
-        <f aca="false">H18-A18</f>
-        <v>0</v>
+        <f aca="false">IF(H18="","",H18-A18)</f>
+        <v>7</v>
       </c>
       <c r="K18" s="18" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="L18" s="18" t="s">
-        <v>122</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="M18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="n">
         <v>46295</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>46298</v>
+        <v>46295</v>
       </c>
       <c r="I19" s="17" t="n">
         <f aca="false">IF(OR(ISNUMBER(SEARCH("Won",F19)),G19="Won"),1,0)</f>
         <v>0</v>
       </c>
       <c r="J19" s="17" t="n">
-        <f aca="false">H19-A19</f>
-        <v>3</v>
+        <f aca="false">IF(H19="","",H19-A19)</f>
+        <v>0</v>
       </c>
       <c r="K19" s="18" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="L19" s="18" t="s">
-        <v>126</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="M19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="n">
-        <v>46297</v>
+        <v>46295</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>46298</v>
@@ -5215,253 +5395,287 @@
         <v>0</v>
       </c>
       <c r="J20" s="17" t="n">
-        <f aca="false">H20-A20</f>
-        <v>1</v>
+        <f aca="false">IF(H20="","",H20-A20)</f>
+        <v>3</v>
       </c>
       <c r="K20" s="18" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="L20" s="18" t="s">
-        <v>130</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="M20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="n">
-        <v>46299</v>
+        <v>46297</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="G21" s="16"/>
+        <v>55</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>82</v>
+      </c>
       <c r="H21" s="15" t="n">
-        <v>46301</v>
+        <v>46298</v>
       </c>
       <c r="I21" s="17" t="n">
         <f aca="false">IF(OR(ISNUMBER(SEARCH("Won",F21)),G21="Won"),1,0)</f>
         <v>0</v>
       </c>
       <c r="J21" s="17" t="n">
-        <f aca="false">H21-A21</f>
-        <v>2</v>
+        <f aca="false">IF(H21="","",H21-A21)</f>
+        <v>1</v>
       </c>
       <c r="K21" s="18" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="L21" s="18" t="s">
-        <v>134</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="M21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="n">
         <v>46299</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>135</v>
+        <v>51</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G22" s="16"/>
       <c r="H22" s="15" t="n">
-        <v>46299</v>
+        <v>46301</v>
       </c>
       <c r="I22" s="17" t="n">
         <f aca="false">IF(OR(ISNUMBER(SEARCH("Won",F22)),G22="Won"),1,0)</f>
         <v>0</v>
       </c>
       <c r="J22" s="17" t="n">
-        <f aca="false">H22-A22</f>
-        <v>0</v>
+        <f aca="false">IF(H22="","",H22-A22)</f>
+        <v>2</v>
       </c>
       <c r="K22" s="18" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L22" s="18" t="s">
-        <v>139</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="M22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="n">
-        <v>46307</v>
+        <v>46299</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="G23" s="16" t="s">
-        <v>143</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="G23" s="16"/>
       <c r="H23" s="15" t="n">
-        <v>46307</v>
+        <v>46299</v>
       </c>
       <c r="I23" s="17" t="n">
         <f aca="false">IF(OR(ISNUMBER(SEARCH("Won",F23)),G23="Won"),1,0)</f>
         <v>0</v>
       </c>
       <c r="J23" s="17" t="n">
-        <f aca="false">H23-A23</f>
+        <f aca="false">IF(H23="","",H23-A23)</f>
         <v>0</v>
       </c>
       <c r="K23" s="18" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="L23" s="18" t="s">
-        <v>145</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="M23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="n">
-        <v>46312</v>
+        <v>46307</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>47</v>
+        <v>149</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>143</v>
+        <v>11</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>46312</v>
+        <v>46307</v>
       </c>
       <c r="I24" s="17" t="n">
         <f aca="false">IF(OR(ISNUMBER(SEARCH("Won",F24)),G24="Won"),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="17" t="n">
-        <f aca="false">H24-A24</f>
+        <f aca="false">IF(H24="","",H24-A24)</f>
         <v>0</v>
       </c>
       <c r="K24" s="18" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="L24" s="18" t="s">
-        <v>149</v>
+        <v>153</v>
+      </c>
+      <c r="M24" s="15" t="n">
+        <v>46308</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="n">
-        <v>46314</v>
+        <v>46312</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>89</v>
+        <v>51</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="G25" s="16"/>
+        <v>55</v>
+      </c>
+      <c r="G25" s="16" t="s">
+        <v>156</v>
+      </c>
       <c r="H25" s="15" t="n">
-        <v>46314</v>
+        <v>46312</v>
       </c>
       <c r="I25" s="17" t="n">
         <f aca="false">IF(OR(ISNUMBER(SEARCH("Won",F25)),G25="Won"),1,0)</f>
         <v>0</v>
       </c>
       <c r="J25" s="17" t="n">
-        <f aca="false">H25-A25</f>
+        <f aca="false">IF(H25="","",H25-A25)</f>
         <v>0</v>
       </c>
       <c r="K25" s="18" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="L25" s="18" t="s">
-        <v>153</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="M25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="19" t="n">
-        <f aca="false">COUNTA(D2:D25)</f>
-        <v>24</v>
-      </c>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="19" t="n">
-        <f aca="false">SUM(I2:I25)</f>
-        <v>1</v>
-      </c>
-      <c r="J26" s="21" t="n">
-        <f aca="false">AVERAGE(J2:J25)</f>
+      <c r="A26" s="15" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G26" s="16"/>
+      <c r="H26" s="15" t="n">
+        <v>46314</v>
+      </c>
+      <c r="I26" s="17" t="n">
+        <f aca="false">IF(OR(ISNUMBER(SEARCH("Won",F26)),G26="Won"),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J26" s="17" t="n">
+        <f aca="false">IF(H26="","",H26-A26)</f>
+        <v>0</v>
+      </c>
+      <c r="K26" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="L26" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="M26" s="2"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="19" t="n">
+        <f aca="false">COUNTA(D2:D26)</f>
+        <v>25</v>
+      </c>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="19" t="n">
+        <f aca="false">SUM(I2:I26)</f>
+        <v>3</v>
+      </c>
+      <c r="J27" s="21" t="n">
+        <f aca="false">AVERAGE(J2:J26)</f>
         <v>4.25</v>
       </c>
-      <c r="K26" s="20"/>
-      <c r="L26" s="20"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
+      <c r="K27" s="20"/>
+      <c r="L27" s="20"/>
+      <c r="M27" s="20"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
-        <v>155</v>
-      </c>
+      <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
@@ -5473,6 +5687,24 @@
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -5494,36 +5726,38 @@
     <hyperlink ref="L9" r:id="rId17" display="https://app.notion.com/p/3c3bd8b60a6381c485e8f231672ce4c5"/>
     <hyperlink ref="K10" r:id="rId18" display="https://app.notion.com/p/3c5bd8b60a6380f9beffec7f6ebf7bcc"/>
     <hyperlink ref="L10" r:id="rId19" display="https://app.notion.com/p/3c9bd8b60a6381bcb17ee7bea7f0dbd1"/>
-    <hyperlink ref="K11" r:id="rId20" display="https://app.notion.com/p/3d1bd8b60a6380f8b80af7ded3b1d693"/>
-    <hyperlink ref="L11" r:id="rId21" display="https://app.notion.com/p/3d3bd8b60a63812c9b83c241d0759778"/>
-    <hyperlink ref="K12" r:id="rId22" display="https://app.notion.com/p/3d2bd8b60a6380239fbbf2e5caf3535b"/>
-    <hyperlink ref="L12" r:id="rId23" display="https://app.notion.com/p/3d3bd8b60a6381b88a86eeb3ed090c66"/>
-    <hyperlink ref="K13" r:id="rId24" display="https://app.notion.com/p/3d7bd8b60a6380d09a13c7ea99f5c73d"/>
-    <hyperlink ref="L13" r:id="rId25" display="https://app.notion.com/p/3ddbd8b60a638178b0c7e3683708efe0"/>
-    <hyperlink ref="K14" r:id="rId26" display="https://app.notion.com/p/3dcbd8b60a6380e2b52cf7954feedfe4"/>
-    <hyperlink ref="L14" r:id="rId27" display="https://app.notion.com/p/3ddbd8b60a6381baa7b1f0a2af8af605"/>
-    <hyperlink ref="K15" r:id="rId28" display="https://app.notion.com/p/3ddbd8b60a6380b3ac7afeb14ac92545"/>
-    <hyperlink ref="L15" r:id="rId29" display="https://app.notion.com/p/3dfbd8b60a638185ab0cec5a8d146a51"/>
-    <hyperlink ref="K16" r:id="rId30" display="https://app.notion.com/p/3e2bd8b60a6380dd8ae2d1f13da0c938"/>
-    <hyperlink ref="L16" r:id="rId31" display="https://app.notion.com/p/3e2bd8b60a63819d908fe4dfdd23e43a"/>
-    <hyperlink ref="K17" r:id="rId32" display="https://app.notion.com/p/3e6bd8b60a63805f9b19cbdf75e9db07"/>
-    <hyperlink ref="L17" r:id="rId33" display="https://app.notion.com/p/3edbd8b60a6381beaaefdda254fc9bdd"/>
-    <hyperlink ref="K18" r:id="rId34" display="https://app.notion.com/p/3ebbd8b60a63806baf49fc5adfddb1f7"/>
-    <hyperlink ref="L18" r:id="rId35" display="https://app.notion.com/p/3ebbd8b60a6381d8b49ae30dfc77e68f"/>
-    <hyperlink ref="K19" r:id="rId36" display="https://app.notion.com/p/3ebbd8b60a63809a96abd3aef15d0a3a"/>
-    <hyperlink ref="L19" r:id="rId37" display="https://app.notion.com/p/3edbd8b60a638155a8bbc9626f125089"/>
-    <hyperlink ref="K20" r:id="rId38" display="https://app.notion.com/p/3edbd8b60a6380be9060ed914eb29833"/>
-    <hyperlink ref="L20" r:id="rId39" display="https://app.notion.com/p/3edbd8b60a63819291d2cda5658a5b85"/>
-    <hyperlink ref="K21" r:id="rId40" display="https://app.notion.com/p/3efbd8b60a638082810dc2c800331cd9"/>
-    <hyperlink ref="L21" r:id="rId41" display="https://app.notion.com/p/3f1bd8b60a638190b44fd0aa570788e3"/>
-    <hyperlink ref="K22" r:id="rId42" display="https://app.notion.com/p/3efbd8b60a6380c89a41ed9957e880d0"/>
-    <hyperlink ref="L22" r:id="rId43" display="https://app.notion.com/p/3efbd8b60a638180a8fdceec5de0cf41"/>
-    <hyperlink ref="K23" r:id="rId44" display="https://app.notion.com/p/3f7bd8b60a638005ac71ff3702d1cc69"/>
-    <hyperlink ref="L23" r:id="rId45" display="https://app.notion.com/p/3f7bd8b60a6381a98a0beffc50495ba7"/>
-    <hyperlink ref="K24" r:id="rId46" display="https://app.notion.com/p/3fbbd8b60a6380cfa966da65cf868718"/>
-    <hyperlink ref="L24" r:id="rId47" display="https://app.notion.com/p/3fcbd8b60a63818fb584f73da73ebad6"/>
-    <hyperlink ref="K25" r:id="rId48" display="https://app.notion.com/p/3febd8b60a63802fa6f7e12a6dba6554"/>
-    <hyperlink ref="L25" r:id="rId49" display="https://app.notion.com/p/3febd8b60a6381deb4bef9ab2288aa08"/>
+    <hyperlink ref="K11" r:id="rId20" display="https://app.notion.com/p/3ffbd8b60a638145bda3f714ba95b244"/>
+    <hyperlink ref="L11" r:id="rId21" display="https://app.notion.com/p/3ffbd8b60a6381b08276f6ac45a7b9f9"/>
+    <hyperlink ref="K12" r:id="rId22" display="https://app.notion.com/p/3d1bd8b60a6380f8b80af7ded3b1d693"/>
+    <hyperlink ref="L12" r:id="rId23" display="https://app.notion.com/p/3d3bd8b60a63812c9b83c241d0759778"/>
+    <hyperlink ref="K13" r:id="rId24" display="https://app.notion.com/p/3d2bd8b60a6380239fbbf2e5caf3535b"/>
+    <hyperlink ref="L13" r:id="rId25" display="https://app.notion.com/p/3d3bd8b60a6381b88a86eeb3ed090c66"/>
+    <hyperlink ref="K14" r:id="rId26" display="https://app.notion.com/p/3d7bd8b60a6380d09a13c7ea99f5c73d"/>
+    <hyperlink ref="L14" r:id="rId27" display="https://app.notion.com/p/3ddbd8b60a638178b0c7e3683708efe0"/>
+    <hyperlink ref="K15" r:id="rId28" display="https://app.notion.com/p/3dcbd8b60a6380e2b52cf7954feedfe4"/>
+    <hyperlink ref="L15" r:id="rId29" display="https://app.notion.com/p/3ddbd8b60a6381baa7b1f0a2af8af605"/>
+    <hyperlink ref="K16" r:id="rId30" display="https://app.notion.com/p/3ddbd8b60a6380b3ac7afeb14ac92545"/>
+    <hyperlink ref="L16" r:id="rId31" display="https://app.notion.com/p/3dfbd8b60a638185ab0cec5a8d146a51"/>
+    <hyperlink ref="K17" r:id="rId32" display="https://app.notion.com/p/3e2bd8b60a6380dd8ae2d1f13da0c938"/>
+    <hyperlink ref="L17" r:id="rId33" display="https://app.notion.com/p/3e2bd8b60a63819d908fe4dfdd23e43a"/>
+    <hyperlink ref="K18" r:id="rId34" display="https://app.notion.com/p/3e6bd8b60a63805f9b19cbdf75e9db07"/>
+    <hyperlink ref="L18" r:id="rId35" display="https://app.notion.com/p/3edbd8b60a6381beaaefdda254fc9bdd"/>
+    <hyperlink ref="K19" r:id="rId36" display="https://app.notion.com/p/3ebbd8b60a63806baf49fc5adfddb1f7"/>
+    <hyperlink ref="L19" r:id="rId37" display="https://app.notion.com/p/3ebbd8b60a6381d8b49ae30dfc77e68f"/>
+    <hyperlink ref="K20" r:id="rId38" display="https://app.notion.com/p/3ebbd8b60a63809a96abd3aef15d0a3a"/>
+    <hyperlink ref="L20" r:id="rId39" display="https://app.notion.com/p/3edbd8b60a638155a8bbc9626f125089"/>
+    <hyperlink ref="K21" r:id="rId40" display="https://app.notion.com/p/3edbd8b60a6380be9060ed914eb29833"/>
+    <hyperlink ref="L21" r:id="rId41" display="https://app.notion.com/p/3edbd8b60a63819291d2cda5658a5b85"/>
+    <hyperlink ref="K22" r:id="rId42" display="https://app.notion.com/p/3efbd8b60a638082810dc2c800331cd9"/>
+    <hyperlink ref="L22" r:id="rId43" display="https://app.notion.com/p/3f1bd8b60a638190b44fd0aa570788e3"/>
+    <hyperlink ref="K23" r:id="rId44" display="https://app.notion.com/p/3efbd8b60a6380c89a41ed9957e880d0"/>
+    <hyperlink ref="L23" r:id="rId45" display="https://app.notion.com/p/3efbd8b60a638180a8fdceec5de0cf41"/>
+    <hyperlink ref="K24" r:id="rId46" display="https://app.notion.com/p/3f7bd8b60a638005ac71ff3702d1cc69"/>
+    <hyperlink ref="L24" r:id="rId47" display="https://app.notion.com/p/3f7bd8b60a6381a98a0beffc50495ba7"/>
+    <hyperlink ref="K25" r:id="rId48" display="https://app.notion.com/p/3fbbd8b60a6380cfa966da65cf868718"/>
+    <hyperlink ref="L25" r:id="rId49" display="https://app.notion.com/p/3fcbd8b60a63818fb584f73da73ebad6"/>
+    <hyperlink ref="K26" r:id="rId50" display="https://app.notion.com/p/3febd8b60a63802fa6f7e12a6dba6554"/>
+    <hyperlink ref="L26" r:id="rId51" display="https://app.notion.com/p/3febd8b60a6381deb4bef9ab2288aa08"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -5532,7 +5766,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <legacyDrawing r:id="rId50"/>
+  <legacyDrawing r:id="rId52"/>
 </worksheet>
 </file>
 
@@ -5555,16 +5789,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>10</v>
@@ -5573,7 +5807,7 @@
         <v>11</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5581,10 +5815,10 @@
         <v>46023</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="D2" s="16" t="n">
         <v>57</v>
@@ -5596,7 +5830,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5604,10 +5838,10 @@
         <v>46023</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D3" s="16" t="n">
         <v>87</v>
@@ -5619,7 +5853,7 @@
         <v>2</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5627,10 +5861,10 @@
         <v>46023</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="D4" s="16" t="n">
         <v>45</v>
@@ -5642,7 +5876,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5650,10 +5884,10 @@
         <v>46023</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D5" s="16" t="n">
         <v>142</v>
@@ -5665,7 +5899,7 @@
         <v>3</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5673,10 +5907,10 @@
         <v>46023</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="D6" s="16" t="n">
         <v>3</v>
@@ -5688,7 +5922,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5696,10 +5930,10 @@
         <v>46023</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="D7" s="16" t="n">
         <v>1</v>
@@ -5711,7 +5945,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5719,10 +5953,10 @@
         <v>46054</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="D8" s="16" t="n">
         <v>41</v>
@@ -5734,7 +5968,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5742,10 +5976,10 @@
         <v>46054</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D9" s="16" t="n">
         <v>123</v>
@@ -5757,7 +5991,7 @@
         <v>4</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5765,10 +5999,10 @@
         <v>46054</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="D10" s="16" t="n">
         <v>47</v>
@@ -5780,7 +6014,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5788,10 +6022,10 @@
         <v>46054</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D11" s="16" t="n">
         <v>143</v>
@@ -5803,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5811,10 +6045,10 @@
         <v>46054</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="D12" s="16" t="n">
         <v>2</v>
@@ -5826,7 +6060,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5834,10 +6068,10 @@
         <v>46054</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="D13" s="16" t="n">
         <v>2</v>
@@ -5849,7 +6083,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5857,10 +6091,10 @@
         <v>46082</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="D14" s="16" t="n">
         <v>26</v>
@@ -5872,7 +6106,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5880,10 +6114,10 @@
         <v>46082</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D15" s="16" t="n">
         <v>85</v>
@@ -5895,7 +6129,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5903,10 +6137,10 @@
         <v>46082</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="D16" s="16" t="n">
         <v>33</v>
@@ -5918,7 +6152,7 @@
         <v>1</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5926,10 +6160,10 @@
         <v>46082</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D17" s="16" t="n">
         <v>95</v>
@@ -5941,7 +6175,7 @@
         <v>1</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5949,10 +6183,10 @@
         <v>46082</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="D18" s="16" t="n">
         <v>1</v>
@@ -5964,7 +6198,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5972,10 +6206,10 @@
         <v>46113</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="D19" s="16" t="n">
         <v>36</v>
@@ -5987,7 +6221,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5995,10 +6229,10 @@
         <v>46113</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D20" s="16" t="n">
         <v>87</v>
@@ -6010,7 +6244,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6018,10 +6252,10 @@
         <v>46113</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="D21" s="16" t="n">
         <v>43</v>
@@ -6033,7 +6267,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6041,10 +6275,10 @@
         <v>46113</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D22" s="16" t="n">
         <v>150</v>
@@ -6056,7 +6290,7 @@
         <v>1</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6064,10 +6298,10 @@
         <v>46113</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="D23" s="16" t="n">
         <v>5</v>
@@ -6079,7 +6313,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6087,10 +6321,10 @@
         <v>46143</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="D24" s="16" t="n">
         <v>35</v>
@@ -6102,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6110,10 +6344,10 @@
         <v>46143</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D25" s="16" t="n">
         <v>54</v>
@@ -6125,7 +6359,7 @@
         <v>2</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6133,10 +6367,10 @@
         <v>46143</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="D26" s="16" t="n">
         <v>43</v>
@@ -6148,7 +6382,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6156,10 +6390,10 @@
         <v>46143</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D27" s="16" t="n">
         <v>157</v>
@@ -6171,7 +6405,7 @@
         <v>4</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6179,10 +6413,10 @@
         <v>46143</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="D28" s="16" t="n">
         <v>29</v>
@@ -6194,7 +6428,7 @@
         <v>1</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6202,10 +6436,10 @@
         <v>46174</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="D29" s="16" t="n">
         <v>39</v>
@@ -6217,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6225,10 +6459,10 @@
         <v>46174</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D30" s="16" t="n">
         <v>57</v>
@@ -6240,7 +6474,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6248,10 +6482,10 @@
         <v>46174</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="D31" s="16" t="n">
         <v>20</v>
@@ -6263,7 +6497,7 @@
         <v>1</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6271,10 +6505,10 @@
         <v>46174</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D32" s="16" t="n">
         <v>142</v>
@@ -6286,7 +6520,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6294,10 +6528,10 @@
         <v>46174</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="D33" s="16" t="n">
         <v>22</v>
@@ -6309,7 +6543,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6317,10 +6551,10 @@
         <v>46204</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="D34" s="16" t="n">
         <v>34</v>
@@ -6332,7 +6566,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6340,10 +6574,10 @@
         <v>46204</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D35" s="16" t="n">
         <v>56</v>
@@ -6355,7 +6589,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6363,10 +6597,10 @@
         <v>46204</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="D36" s="16" t="n">
         <v>15</v>
@@ -6378,7 +6612,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6386,10 +6620,10 @@
         <v>46204</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D37" s="16" t="n">
         <v>109</v>
@@ -6401,7 +6635,7 @@
         <v>2</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6409,10 +6643,10 @@
         <v>46204</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="D38" s="16" t="n">
         <v>36</v>
@@ -6424,7 +6658,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6432,20 +6666,20 @@
         <v>46235</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="D39" s="16" t="n">
         <v>17</v>
       </c>
       <c r="E39" s="17" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A39,Interviews!$A$2:$A$25,"&lt;"&amp;EDATE(A39,1),Interviews!$B$2:$B$25,C39)</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A39,Interviews!$A$2:$A$26,"&lt;"&amp;EDATE(A39,1),Interviews!$B$2:$B$26,C39)</f>
         <v>0</v>
       </c>
       <c r="F39" s="17" t="n">
-        <f aca="false">SUMIFS(Interviews!$I$2:$I$25,Interviews!$A$2:$A$25,"&gt;="&amp;A39,Interviews!$A$2:$A$25,"&lt;"&amp;EDATE(A39,1),Interviews!$B$2:$B$25,C39)</f>
+        <f aca="false">SUMIFS(Interviews!$I$2:$I$26,Interviews!$A$2:$A$26,"&gt;="&amp;A39,Interviews!$A$2:$A$26,"&lt;"&amp;EDATE(A39,1),Interviews!$B$2:$B$26,C39)</f>
         <v>0</v>
       </c>
       <c r="G39" s="16" t="s">
@@ -6457,20 +6691,20 @@
         <v>46235</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D40" s="16" t="n">
         <v>36</v>
       </c>
       <c r="E40" s="17" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A40,Interviews!$A$2:$A$25,"&lt;"&amp;EDATE(A40,1),Interviews!$B$2:$B$25,C40)</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A40,Interviews!$A$2:$A$26,"&lt;"&amp;EDATE(A40,1),Interviews!$B$2:$B$26,C40)</f>
         <v>0</v>
       </c>
       <c r="F40" s="17" t="n">
-        <f aca="false">SUMIFS(Interviews!$I$2:$I$25,Interviews!$A$2:$A$25,"&gt;="&amp;A40,Interviews!$A$2:$A$25,"&lt;"&amp;EDATE(A40,1),Interviews!$B$2:$B$25,C40)</f>
+        <f aca="false">SUMIFS(Interviews!$I$2:$I$26,Interviews!$A$2:$A$26,"&gt;="&amp;A40,Interviews!$A$2:$A$26,"&lt;"&amp;EDATE(A40,1),Interviews!$B$2:$B$26,C40)</f>
         <v>0</v>
       </c>
       <c r="G40" s="16" t="s">
@@ -6482,20 +6716,20 @@
         <v>46235</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="D41" s="16" t="n">
         <v>12</v>
       </c>
       <c r="E41" s="17" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A41,Interviews!$A$2:$A$25,"&lt;"&amp;EDATE(A41,1),Interviews!$B$2:$B$25,C41)</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A41,Interviews!$A$2:$A$26,"&lt;"&amp;EDATE(A41,1),Interviews!$B$2:$B$26,C41)</f>
         <v>0</v>
       </c>
       <c r="F41" s="17" t="n">
-        <f aca="false">SUMIFS(Interviews!$I$2:$I$25,Interviews!$A$2:$A$25,"&gt;="&amp;A41,Interviews!$A$2:$A$25,"&lt;"&amp;EDATE(A41,1),Interviews!$B$2:$B$25,C41)</f>
+        <f aca="false">SUMIFS(Interviews!$I$2:$I$26,Interviews!$A$2:$A$26,"&gt;="&amp;A41,Interviews!$A$2:$A$26,"&lt;"&amp;EDATE(A41,1),Interviews!$B$2:$B$26,C41)</f>
         <v>0</v>
       </c>
       <c r="G41" s="16" t="s">
@@ -6507,20 +6741,20 @@
         <v>46235</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D42" s="16" t="n">
         <v>105</v>
       </c>
       <c r="E42" s="17" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A42,Interviews!$A$2:$A$25,"&lt;"&amp;EDATE(A42,1),Interviews!$B$2:$B$25,C42)</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A42,Interviews!$A$2:$A$26,"&lt;"&amp;EDATE(A42,1),Interviews!$B$2:$B$26,C42)</f>
         <v>9</v>
       </c>
       <c r="F42" s="17" t="n">
-        <f aca="false">SUMIFS(Interviews!$I$2:$I$25,Interviews!$A$2:$A$25,"&gt;="&amp;A42,Interviews!$A$2:$A$25,"&lt;"&amp;EDATE(A42,1),Interviews!$B$2:$B$25,C42)</f>
+        <f aca="false">SUMIFS(Interviews!$I$2:$I$26,Interviews!$A$2:$A$26,"&gt;="&amp;A42,Interviews!$A$2:$A$26,"&lt;"&amp;EDATE(A42,1),Interviews!$B$2:$B$26,C42)</f>
         <v>0</v>
       </c>
       <c r="G42" s="16" t="s">
@@ -6532,20 +6766,20 @@
         <v>46266</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="D43" s="16" t="n">
         <v>14</v>
       </c>
       <c r="E43" s="17" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A43,Interviews!$A$2:$A$25,"&lt;"&amp;EDATE(A43,1),Interviews!$B$2:$B$25,C43)</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A43,Interviews!$A$2:$A$26,"&lt;"&amp;EDATE(A43,1),Interviews!$B$2:$B$26,C43)</f>
         <v>0</v>
       </c>
       <c r="F43" s="17" t="n">
-        <f aca="false">SUMIFS(Interviews!$I$2:$I$25,Interviews!$A$2:$A$25,"&gt;="&amp;A43,Interviews!$A$2:$A$25,"&lt;"&amp;EDATE(A43,1),Interviews!$B$2:$B$25,C43)</f>
+        <f aca="false">SUMIFS(Interviews!$I$2:$I$26,Interviews!$A$2:$A$26,"&gt;="&amp;A43,Interviews!$A$2:$A$26,"&lt;"&amp;EDATE(A43,1),Interviews!$B$2:$B$26,C43)</f>
         <v>0</v>
       </c>
       <c r="G43" s="16" t="s">
@@ -6557,21 +6791,21 @@
         <v>46266</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D44" s="16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E44" s="17" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A44,Interviews!$A$2:$A$25,"&lt;"&amp;EDATE(A44,1),Interviews!$B$2:$B$25,C44)</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A44,Interviews!$A$2:$A$26,"&lt;"&amp;EDATE(A44,1),Interviews!$B$2:$B$26,C44)</f>
+        <v>3</v>
+      </c>
+      <c r="F44" s="17" t="n">
+        <f aca="false">SUMIFS(Interviews!$I$2:$I$26,Interviews!$A$2:$A$26,"&gt;="&amp;A44,Interviews!$A$2:$A$26,"&lt;"&amp;EDATE(A44,1),Interviews!$B$2:$B$26,C44)</f>
         <v>2</v>
-      </c>
-      <c r="F44" s="17" t="n">
-        <f aca="false">SUMIFS(Interviews!$I$2:$I$25,Interviews!$A$2:$A$25,"&gt;="&amp;A44,Interviews!$A$2:$A$25,"&lt;"&amp;EDATE(A44,1),Interviews!$B$2:$B$25,C44)</f>
-        <v>1</v>
       </c>
       <c r="G44" s="16" t="s">
         <v>3</v>
@@ -6582,20 +6816,20 @@
         <v>46266</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="D45" s="16" t="n">
         <v>21</v>
       </c>
       <c r="E45" s="17" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A45,Interviews!$A$2:$A$25,"&lt;"&amp;EDATE(A45,1),Interviews!$B$2:$B$25,C45)</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A45,Interviews!$A$2:$A$26,"&lt;"&amp;EDATE(A45,1),Interviews!$B$2:$B$26,C45)</f>
         <v>0</v>
       </c>
       <c r="F45" s="17" t="n">
-        <f aca="false">SUMIFS(Interviews!$I$2:$I$25,Interviews!$A$2:$A$25,"&gt;="&amp;A45,Interviews!$A$2:$A$25,"&lt;"&amp;EDATE(A45,1),Interviews!$B$2:$B$25,C45)</f>
+        <f aca="false">SUMIFS(Interviews!$I$2:$I$26,Interviews!$A$2:$A$26,"&gt;="&amp;A45,Interviews!$A$2:$A$26,"&lt;"&amp;EDATE(A45,1),Interviews!$B$2:$B$26,C45)</f>
         <v>0</v>
       </c>
       <c r="G45" s="16" t="s">
@@ -6607,20 +6841,20 @@
         <v>46266</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D46" s="16" t="n">
         <v>108</v>
       </c>
       <c r="E46" s="17" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A46,Interviews!$A$2:$A$25,"&lt;"&amp;EDATE(A46,1),Interviews!$B$2:$B$25,C46)</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A46,Interviews!$A$2:$A$26,"&lt;"&amp;EDATE(A46,1),Interviews!$B$2:$B$26,C46)</f>
         <v>7</v>
       </c>
       <c r="F46" s="17" t="n">
-        <f aca="false">SUMIFS(Interviews!$I$2:$I$25,Interviews!$A$2:$A$25,"&gt;="&amp;A46,Interviews!$A$2:$A$25,"&lt;"&amp;EDATE(A46,1),Interviews!$B$2:$B$25,C46)</f>
+        <f aca="false">SUMIFS(Interviews!$I$2:$I$26,Interviews!$A$2:$A$26,"&gt;="&amp;A46,Interviews!$A$2:$A$26,"&lt;"&amp;EDATE(A46,1),Interviews!$B$2:$B$26,C46)</f>
         <v>0</v>
       </c>
       <c r="G46" s="16" t="s">
@@ -6632,20 +6866,20 @@
         <v>46296</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="D47" s="16" t="n">
         <v>10</v>
       </c>
       <c r="E47" s="17" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A47,Interviews!$A$2:$A$25,"&lt;"&amp;EDATE(A47,1),Interviews!$B$2:$B$25,C47)</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A47,Interviews!$A$2:$A$26,"&lt;"&amp;EDATE(A47,1),Interviews!$B$2:$B$26,C47)</f>
         <v>1</v>
       </c>
       <c r="F47" s="17" t="n">
-        <f aca="false">SUMIFS(Interviews!$I$2:$I$25,Interviews!$A$2:$A$25,"&gt;="&amp;A47,Interviews!$A$2:$A$25,"&lt;"&amp;EDATE(A47,1),Interviews!$B$2:$B$25,C47)</f>
+        <f aca="false">SUMIFS(Interviews!$I$2:$I$26,Interviews!$A$2:$A$26,"&gt;="&amp;A47,Interviews!$A$2:$A$26,"&lt;"&amp;EDATE(A47,1),Interviews!$B$2:$B$26,C47)</f>
         <v>0</v>
       </c>
       <c r="G47" s="16" t="s">
@@ -6657,20 +6891,20 @@
         <v>46296</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D48" s="16" t="n">
         <v>32</v>
       </c>
       <c r="E48" s="17" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A48,Interviews!$A$2:$A$25,"&lt;"&amp;EDATE(A48,1),Interviews!$B$2:$B$25,C48)</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A48,Interviews!$A$2:$A$26,"&lt;"&amp;EDATE(A48,1),Interviews!$B$2:$B$26,C48)</f>
         <v>1</v>
       </c>
       <c r="F48" s="17" t="n">
-        <f aca="false">SUMIFS(Interviews!$I$2:$I$25,Interviews!$A$2:$A$25,"&gt;="&amp;A48,Interviews!$A$2:$A$25,"&lt;"&amp;EDATE(A48,1),Interviews!$B$2:$B$25,C48)</f>
+        <f aca="false">SUMIFS(Interviews!$I$2:$I$26,Interviews!$A$2:$A$26,"&gt;="&amp;A48,Interviews!$A$2:$A$26,"&lt;"&amp;EDATE(A48,1),Interviews!$B$2:$B$26,C48)</f>
         <v>0</v>
       </c>
       <c r="G48" s="16" t="s">
@@ -6682,21 +6916,21 @@
         <v>46296</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="D49" s="16" t="n">
         <v>15</v>
       </c>
       <c r="E49" s="17" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A49,Interviews!$A$2:$A$25,"&lt;"&amp;EDATE(A49,1),Interviews!$B$2:$B$25,C49)</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A49,Interviews!$A$2:$A$26,"&lt;"&amp;EDATE(A49,1),Interviews!$B$2:$B$26,C49)</f>
         <v>1</v>
       </c>
       <c r="F49" s="17" t="n">
-        <f aca="false">SUMIFS(Interviews!$I$2:$I$25,Interviews!$A$2:$A$25,"&gt;="&amp;A49,Interviews!$A$2:$A$25,"&lt;"&amp;EDATE(A49,1),Interviews!$B$2:$B$25,C49)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(Interviews!$I$2:$I$26,Interviews!$A$2:$A$26,"&gt;="&amp;A49,Interviews!$A$2:$A$26,"&lt;"&amp;EDATE(A49,1),Interviews!$B$2:$B$26,C49)</f>
+        <v>1</v>
       </c>
       <c r="G49" s="16" t="s">
         <v>3</v>
@@ -6707,20 +6941,20 @@
         <v>46296</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D50" s="16" t="n">
         <v>75</v>
       </c>
       <c r="E50" s="17" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A50,Interviews!$A$2:$A$25,"&lt;"&amp;EDATE(A50,1),Interviews!$B$2:$B$25,C50)</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A50,Interviews!$A$2:$A$26,"&lt;"&amp;EDATE(A50,1),Interviews!$B$2:$B$26,C50)</f>
         <v>3</v>
       </c>
       <c r="F50" s="17" t="n">
-        <f aca="false">SUMIFS(Interviews!$I$2:$I$25,Interviews!$A$2:$A$25,"&gt;="&amp;A50,Interviews!$A$2:$A$25,"&lt;"&amp;EDATE(A50,1),Interviews!$B$2:$B$25,C50)</f>
+        <f aca="false">SUMIFS(Interviews!$I$2:$I$26,Interviews!$A$2:$A$26,"&gt;="&amp;A50,Interviews!$A$2:$A$26,"&lt;"&amp;EDATE(A50,1),Interviews!$B$2:$B$26,C50)</f>
         <v>0</v>
       </c>
       <c r="G50" s="16" t="s">
@@ -6738,7 +6972,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -6780,7 +7014,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6795,7 +7029,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -6823,13 +7057,13 @@
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>10</v>
@@ -6847,13 +7081,13 @@
         <v>17</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>9</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6897,7 +7131,7 @@
         <v>10.8064516129032</v>
       </c>
       <c r="K5" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6941,7 +7175,7 @@
         <v>12.7857142857143</v>
       </c>
       <c r="K6" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6985,7 +7219,7 @@
         <v>7.74193548387097</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7029,7 +7263,7 @@
         <v>10.7</v>
       </c>
       <c r="K8" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7073,7 +7307,7 @@
         <v>10.258064516129</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7117,7 +7351,7 @@
         <v>9.33333333333333</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7161,7 +7395,7 @@
         <v>8.06451612903226</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7218,27 +7452,27 @@
       </c>
       <c r="C13" s="2" t="n">
         <f aca="false">SUMIFS(Data_Monthly!$D$2:$D$50,Data_Monthly!$A$2:$A$50,A13)</f>
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D13" s="2" t="n">
         <f aca="false">SUMIFS(Data_Monthly!$E$2:$E$50,Data_Monthly!$A$2:$A$50,A13)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13" s="2" t="n">
         <f aca="false">SUMIFS(Data_Monthly!$F$2:$F$50,Data_Monthly!$A$2:$A$50,A13)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="11" t="n">
         <f aca="false">IFERROR(D13/C13,0)</f>
-        <v>0.0502793296089386</v>
+        <v>0.0555555555555556</v>
       </c>
       <c r="G13" s="11" t="n">
         <f aca="false">IFERROR(E13/C13,0)</f>
-        <v>0.00558659217877095</v>
+        <v>0.0111111111111111</v>
       </c>
       <c r="H13" s="11" t="n">
         <f aca="false">IFERROR(E13/D13,0)</f>
-        <v>0.111111111111111</v>
+        <v>0.2</v>
       </c>
       <c r="I13" s="2" t="n">
         <f aca="false">DAY(EOMONTH(A13,0))</f>
@@ -7246,7 +7480,7 @@
       </c>
       <c r="J13" s="9" t="n">
         <f aca="false">IFERROR(C13/I13,0)</f>
-        <v>5.96666666666667</v>
+        <v>6</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>3</v>
@@ -7270,7 +7504,7 @@
       </c>
       <c r="E14" s="2" t="n">
         <f aca="false">SUMIFS(Data_Monthly!$F$2:$F$50,Data_Monthly!$A$2:$A$50,A14)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="11" t="n">
         <f aca="false">IFERROR(D14/C14,0)</f>
@@ -7278,11 +7512,11 @@
       </c>
       <c r="G14" s="11" t="n">
         <f aca="false">IFERROR(E14/C14,0)</f>
-        <v>0</v>
+        <v>0.00757575757575758</v>
       </c>
       <c r="H14" s="11" t="n">
         <f aca="false">IFERROR(E14/D14,0)</f>
-        <v>0</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I14" s="16" t="n">
         <v>20</v>
@@ -7311,7 +7545,7 @@
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="20"/>
       <c r="B16" s="19" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="C16" s="19" t="n">
         <f aca="false">SUM(C5:C11)</f>
@@ -7350,31 +7584,31 @@
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20"/>
       <c r="B17" s="19" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="C17" s="19" t="n">
         <f aca="false">SUM(C12:C14)</f>
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D17" s="19" t="n">
         <f aca="false">SUM(D12:D14)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E17" s="19" t="n">
         <f aca="false">SUM(E12:E14)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F17" s="22" t="n">
         <f aca="false">IFERROR(D17/C17,0)</f>
-        <v>0.0498960498960499</v>
+        <v>0.0518672199170125</v>
       </c>
       <c r="G17" s="22" t="n">
         <f aca="false">IFERROR(E17/C17,0)</f>
-        <v>0.00207900207900208</v>
+        <v>0.00622406639004149</v>
       </c>
       <c r="H17" s="22" t="n">
         <f aca="false">IFERROR(E17/D17,0)</f>
-        <v>0.0416666666666667</v>
+        <v>0.12</v>
       </c>
       <c r="I17" s="19" t="n">
         <f aca="false">SUM(I12:I14)</f>
@@ -7382,14 +7616,14 @@
       </c>
       <c r="J17" s="23" t="n">
         <f aca="false">IFERROR(C17/I17,0)</f>
-        <v>5.93827160493827</v>
+        <v>5.95061728395062</v>
       </c>
       <c r="K17" s="20"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="20"/>
       <c r="B18" s="19" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="C18" s="19" t="n">
         <f aca="false">SUM(C7:C11)</f>
@@ -7428,30 +7662,30 @@
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2"/>
       <c r="B19" s="5" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="12" t="n">
         <f aca="false">F17-F16</f>
-        <v>-0.0252704581914858</v>
+        <v>-0.0232992881705232</v>
       </c>
       <c r="G19" s="12" t="n">
         <f aca="false">G17-G16</f>
-        <v>-0.00981443274497509</v>
+        <v>-0.00566936843393567</v>
       </c>
       <c r="H19" s="12" t="n">
         <f aca="false">H17-H16</f>
-        <v>-0.116561181434599</v>
+        <v>-0.0382278481012658</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="10" t="n">
         <f aca="false">J17-J16</f>
-        <v>-3.97682273468437</v>
+        <v>-3.96447705567202</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>
@@ -7472,7 +7706,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
@@ -7494,7 +7728,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7514,7 +7748,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -7552,13 +7786,13 @@
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>10</v>
@@ -7576,33 +7810,33 @@
         <v>17</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B5" s="2" t="n">
         <f aca="false">SUMIFS(Data_Monthly!$D$2:$D$50,Data_Monthly!$C$2:$C$50,A5,Data_Monthly!$A$2:$A$50,"&gt;="&amp;DATE(2026,8,1))</f>
@@ -7610,14 +7844,14 @@
       </c>
       <c r="C5" s="11" t="n">
         <f aca="false">IFERROR(B5/$B$9,0)</f>
-        <v>0.598752598752599</v>
+        <v>0.597510373443983</v>
       </c>
       <c r="D5" s="2" t="n">
-        <f aca="false">COUNTIFS(Interviews!$B$2:$B$25,A5)</f>
+        <f aca="false">COUNTIFS(Interviews!$B$2:$B$26,A5)</f>
         <v>19</v>
       </c>
       <c r="E5" s="2" t="n">
-        <f aca="false">SUMIFS(Interviews!$I$2:$I$25,Interviews!$B$2:$B$25,A5)</f>
+        <f aca="false">SUMIFS(Interviews!$I$2:$I$26,Interviews!$B$2:$B$26,A5)</f>
         <v>0</v>
       </c>
       <c r="F5" s="11" t="n">
@@ -7632,16 +7866,17 @@
         <f aca="false">IFERROR(E5/D5,0)</f>
         <v>0</v>
       </c>
-      <c r="I5" s="16" t="n">
-        <v>285</v>
+      <c r="I5" s="2" t="n">
+        <f aca="false">B5-COUNTIFS(Interviews!$B$2:$B$26,A5,Interviews!$C$2:$C$26,"INVITE")</f>
+        <v>287</v>
       </c>
       <c r="J5" s="2" t="n">
-        <f aca="false">COUNTIFS(Interviews!$B$2:$B$25,A5,Interviews!$C$2:$C$25,"Alex")</f>
-        <v>16</v>
+        <f aca="false">D5-COUNTIFS(Interviews!$B$2:$B$26,A5,Interviews!$C$2:$C$26,"INVITE")</f>
+        <v>18</v>
       </c>
       <c r="K5" s="11" t="n">
         <f aca="false">IFERROR(J5/I5,0)</f>
-        <v>0.056140350877193</v>
+        <v>0.0627177700348432</v>
       </c>
       <c r="L5" s="2" t="n">
         <f aca="false">SUMIFS(Data_Monthly!$D$2:$D$50,Data_Monthly!$C$2:$C$50,A5,Data_Monthly!$A$2:$A$50,"&lt;"&amp;DATE(2026,8,1))</f>
@@ -7666,46 +7901,47 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B6" s="2" t="n">
         <f aca="false">SUMIFS(Data_Monthly!$D$2:$D$50,Data_Monthly!$C$2:$C$50,A6,Data_Monthly!$A$2:$A$50,"&gt;="&amp;DATE(2026,8,1))</f>
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C6" s="11" t="n">
         <f aca="false">IFERROR(B6/$B$9,0)</f>
-        <v>0.216216216216216</v>
+        <v>0.217842323651452</v>
       </c>
       <c r="D6" s="2" t="n">
-        <f aca="false">COUNTIFS(Interviews!$B$2:$B$25,A6)</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Interviews!$B$2:$B$26,A6)</f>
+        <v>4</v>
       </c>
       <c r="E6" s="2" t="n">
-        <f aca="false">SUMIFS(Interviews!$I$2:$I$25,Interviews!$B$2:$B$25,A6)</f>
-        <v>1</v>
+        <f aca="false">SUMIFS(Interviews!$I$2:$I$26,Interviews!$B$2:$B$26,A6)</f>
+        <v>2</v>
       </c>
       <c r="F6" s="11" t="n">
         <f aca="false">IFERROR(D6/B6,0)</f>
-        <v>0.0288461538461538</v>
+        <v>0.0380952380952381</v>
       </c>
       <c r="G6" s="11" t="n">
         <f aca="false">IFERROR(E6/B6,0)</f>
-        <v>0.00961538461538462</v>
+        <v>0.0190476190476191</v>
       </c>
       <c r="H6" s="11" t="n">
         <f aca="false">IFERROR(E6/D6,0)</f>
-        <v>0.333333333333333</v>
-      </c>
-      <c r="I6" s="16" t="n">
-        <v>103</v>
+        <v>0.5</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <f aca="false">B6-COUNTIFS(Interviews!$B$2:$B$26,A6,Interviews!$C$2:$C$26,"INVITE")</f>
+        <v>105</v>
       </c>
       <c r="J6" s="2" t="n">
-        <f aca="false">COUNTIFS(Interviews!$B$2:$B$25,A6,Interviews!$C$2:$C$25,"Alex")</f>
-        <v>2</v>
+        <f aca="false">D6-COUNTIFS(Interviews!$B$2:$B$26,A6,Interviews!$C$2:$C$26,"INVITE")</f>
+        <v>4</v>
       </c>
       <c r="K6" s="11" t="n">
         <f aca="false">IFERROR(J6/I6,0)</f>
-        <v>0.0194174757281553</v>
+        <v>0.0380952380952381</v>
       </c>
       <c r="L6" s="2" t="n">
         <f aca="false">SUMIFS(Data_Monthly!$D$2:$D$50,Data_Monthly!$C$2:$C$50,A6,Data_Monthly!$A$2:$A$50,"&lt;"&amp;DATE(2026,8,1))</f>
@@ -7721,16 +7957,16 @@
       </c>
       <c r="O6" s="12" t="n">
         <f aca="false">F6-N6</f>
-        <v>-0.0421920975199664</v>
+        <v>-0.0329430132708821</v>
       </c>
       <c r="P6" s="2" t="n">
         <f aca="false">RANK(K6,$K$5:$K$8,0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="B7" s="2" t="n">
         <f aca="false">SUMIFS(Data_Monthly!$D$2:$D$50,Data_Monthly!$C$2:$C$50,A7,Data_Monthly!$A$2:$A$50,"&gt;="&amp;DATE(2026,8,1))</f>
@@ -7738,15 +7974,15 @@
       </c>
       <c r="C7" s="11" t="n">
         <f aca="false">IFERROR(B7/$B$9,0)</f>
-        <v>0.0997920997920998</v>
+        <v>0.0995850622406639</v>
       </c>
       <c r="D7" s="2" t="n">
-        <f aca="false">COUNTIFS(Interviews!$B$2:$B$25,A7)</f>
+        <f aca="false">COUNTIFS(Interviews!$B$2:$B$26,A7)</f>
         <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
-        <f aca="false">SUMIFS(Interviews!$I$2:$I$25,Interviews!$B$2:$B$25,A7)</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(Interviews!$I$2:$I$26,Interviews!$B$2:$B$26,A7)</f>
+        <v>1</v>
       </c>
       <c r="F7" s="11" t="n">
         <f aca="false">IFERROR(D7/B7,0)</f>
@@ -7754,22 +7990,23 @@
       </c>
       <c r="G7" s="11" t="n">
         <f aca="false">IFERROR(E7/B7,0)</f>
-        <v>0</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="H7" s="11" t="n">
         <f aca="false">IFERROR(E7/D7,0)</f>
-        <v>0</v>
-      </c>
-      <c r="I7" s="16" t="n">
-        <v>47</v>
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <f aca="false">B7-COUNTIFS(Interviews!$B$2:$B$26,A7,Interviews!$C$2:$C$26,"INVITE")</f>
+        <v>48</v>
       </c>
       <c r="J7" s="2" t="n">
-        <f aca="false">COUNTIFS(Interviews!$B$2:$B$25,A7,Interviews!$C$2:$C$25,"Alex")</f>
-        <v>0</v>
+        <f aca="false">D7-COUNTIFS(Interviews!$B$2:$B$26,A7,Interviews!$C$2:$C$26,"INVITE")</f>
+        <v>1</v>
       </c>
       <c r="K7" s="11" t="n">
         <f aca="false">IFERROR(J7/I7,0)</f>
-        <v>0</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="L7" s="2" t="n">
         <f aca="false">SUMIFS(Data_Monthly!$D$2:$D$50,Data_Monthly!$C$2:$C$50,A7,Data_Monthly!$A$2:$A$50,"&lt;"&amp;DATE(2026,8,1))</f>
@@ -7794,7 +8031,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="B8" s="2" t="n">
         <f aca="false">SUMIFS(Data_Monthly!$D$2:$D$50,Data_Monthly!$C$2:$C$50,A8,Data_Monthly!$A$2:$A$50,"&gt;="&amp;DATE(2026,8,1))</f>
@@ -7802,14 +8039,14 @@
       </c>
       <c r="C8" s="11" t="n">
         <f aca="false">IFERROR(B8/$B$9,0)</f>
-        <v>0.0852390852390852</v>
+        <v>0.0850622406639004</v>
       </c>
       <c r="D8" s="2" t="n">
-        <f aca="false">COUNTIFS(Interviews!$B$2:$B$25,A8)</f>
+        <f aca="false">COUNTIFS(Interviews!$B$2:$B$26,A8)</f>
         <v>1</v>
       </c>
       <c r="E8" s="2" t="n">
-        <f aca="false">SUMIFS(Interviews!$I$2:$I$25,Interviews!$B$2:$B$25,A8)</f>
+        <f aca="false">SUMIFS(Interviews!$I$2:$I$26,Interviews!$B$2:$B$26,A8)</f>
         <v>0</v>
       </c>
       <c r="F8" s="11" t="n">
@@ -7824,11 +8061,12 @@
         <f aca="false">IFERROR(E8/D8,0)</f>
         <v>0</v>
       </c>
-      <c r="I8" s="16" t="n">
+      <c r="I8" s="2" t="n">
+        <f aca="false">B8-COUNTIFS(Interviews!$B$2:$B$26,A8,Interviews!$C$2:$C$26,"INVITE")</f>
         <v>41</v>
       </c>
       <c r="J8" s="2" t="n">
-        <f aca="false">COUNTIFS(Interviews!$B$2:$B$25,A8,Interviews!$C$2:$C$25,"Alex")</f>
+        <f aca="false">D8-COUNTIFS(Interviews!$B$2:$B$26,A8,Interviews!$C$2:$C$26,"INVITE")</f>
         <v>1</v>
       </c>
       <c r="K8" s="11" t="n">
@@ -7853,16 +8091,16 @@
       </c>
       <c r="P8" s="2" t="n">
         <f aca="false">RANK(K8,$K$5:$K$8,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="B9" s="19" t="n">
         <f aca="false">SUM(B5:B8)</f>
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C9" s="22" t="n">
         <f aca="false">SUM(C5:C8)</f>
@@ -7870,35 +8108,35 @@
       </c>
       <c r="D9" s="19" t="n">
         <f aca="false">SUM(D5:D8)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E9" s="19" t="n">
         <f aca="false">SUM(E5:E8)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" s="22" t="n">
         <f aca="false">IFERROR(D9/B9,0)</f>
-        <v>0.0498960498960499</v>
+        <v>0.0518672199170125</v>
       </c>
       <c r="G9" s="22" t="n">
         <f aca="false">IFERROR(E9/B9,0)</f>
-        <v>0.00207900207900208</v>
+        <v>0.00622406639004149</v>
       </c>
       <c r="H9" s="22" t="n">
         <f aca="false">IFERROR(E9/D9,0)</f>
-        <v>0.0416666666666667</v>
+        <v>0.12</v>
       </c>
       <c r="I9" s="19" t="n">
         <f aca="false">SUM(I5:I8)</f>
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="J9" s="19" t="n">
         <f aca="false">SUM(J5:J8)</f>
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K9" s="22" t="n">
         <f aca="false">IFERROR(J9/I9,0)</f>
-        <v>0.0399159663865546</v>
+        <v>0.0498960498960499</v>
       </c>
       <c r="L9" s="19" t="n">
         <f aca="false">SUMIFS(Data_Monthly!$D$2:$D$50,Data_Monthly!$A$2:$A$50,"&lt;"&amp;DATE(2026,8,1))</f>
@@ -7914,7 +8152,7 @@
       </c>
       <c r="O9" s="24" t="n">
         <f aca="false">F9-N9</f>
-        <v>-0.0252704581914858</v>
+        <v>-0.0232992881705232</v>
       </c>
       <c r="P9" s="20"/>
     </row>
@@ -7938,13 +8176,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="n">
-        <f aca="false">Interviews!D26</f>
-        <v>24</v>
+        <f aca="false">Interviews!D27</f>
+        <v>25</v>
       </c>
       <c r="E11" s="2" t="str">
         <f aca="false">IF(D11=D9,"OK","MISMATCH")</f>
@@ -7964,16 +8202,16 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="n">
         <f aca="false">B9-I9</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E12" s="2" t="str">
-        <f aca="false">IF(D12=COUNTIFS(Interviews!$C$2:$C$25,"&lt;&gt;Alex"),"OK","MISMATCH")</f>
+        <f aca="false">IF(D12=COUNTIFS(Interviews!$C$2:$C$26,"INVITE"),"OK","MISMATCH")</f>
         <v>OK</v>
       </c>
       <c r="F12" s="2"/>
@@ -8008,7 +8246,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B14" s="2" t="str">
         <f aca="false">INDEX($A$5:$A$8,MATCH(MAX($B$5:$B$8),$B$5:$B$8,0))</f>
@@ -8019,7 +8257,7 @@
         <v>288</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
@@ -8036,7 +8274,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B15" s="2" t="str">
         <f aca="false">INDEX($A$5:$A$8,MATCH(MAX($K$5:$K$8),$K$5:$K$8,0))</f>
@@ -8044,7 +8282,7 @@
       </c>
       <c r="C15" s="11" t="n">
         <f aca="false">MAX(K5:K8)</f>
-        <v>0.056140350877193</v>
+        <v>0.0627177700348432</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -8062,18 +8300,18 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="B16" s="2" t="str">
         <f aca="false">INDEX($A$5:$A$8,MATCH(MAX($G$5:$G$8),$G$5:$G$8,0))</f>
-        <v>Polina</v>
+        <v>Shevk</v>
       </c>
       <c r="C16" s="25" t="n">
         <f aca="false">MAX(G5:G8)</f>
-        <v>0.00961538461538462</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
@@ -8087,6 +8325,210 @@
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+    </row>
+    <row r="19" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <f aca="false">B9-B21-B22</f>
+        <v>476</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <f aca="false">COUNTIFS(Interviews!$C$2:$C$26,A20)</f>
+        <v>19</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <f aca="false">SUMIFS(Interviews!$I$2:$I$26,Interviews!$C$2:$C$26,A20)</f>
+        <v>1</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <f aca="false">IFERROR(C20/B20,0)</f>
+        <v>0.0399159663865546</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <f aca="false">IFERROR(D20/B20,0)</f>
+        <v>0.00210084033613445</v>
+      </c>
+      <c r="G20" s="11" t="n">
+        <f aca="false">IFERROR(D20/C20,0)</f>
+        <v>0.0526315789473684</v>
+      </c>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <f aca="false">COUNTIFS(Interviews!$C$2:$C$26,A21)</f>
+        <v>5</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <f aca="false">COUNTIFS(Interviews!$C$2:$C$26,A21)</f>
+        <v>5</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <f aca="false">SUMIFS(Interviews!$I$2:$I$26,Interviews!$C$2:$C$26,A21)</f>
+        <v>2</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <f aca="false">IFERROR(C21/B21,0)</f>
+        <v>1</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <f aca="false">IFERROR(D21/B21,0)</f>
+        <v>0.4</v>
+      </c>
+      <c r="G21" s="11" t="n">
+        <f aca="false">IFERROR(D21/C21,0)</f>
+        <v>0.4</v>
+      </c>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <f aca="false">COUNTIFS(Interviews!$C$2:$C$26,A22)</f>
+        <v>1</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <f aca="false">COUNTIFS(Interviews!$C$2:$C$26,A22)</f>
+        <v>1</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <f aca="false">SUMIFS(Interviews!$I$2:$I$26,Interviews!$C$2:$C$26,A22)</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <f aca="false">IFERROR(C22/B22,0)</f>
+        <v>1</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <f aca="false">IFERROR(D22/B22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="11" t="n">
+        <f aca="false">IFERROR(D22/C22,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -8121,7 +8563,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8151,22 +8593,22 @@
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>10</v>
@@ -8178,13 +8620,13 @@
         <v>13</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8208,11 +8650,11 @@
         <v>12</v>
       </c>
       <c r="G4" s="2" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A4,Interviews!$A$2:$A$25,"&lt;"&amp;(A4+7))</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A4,Interviews!$A$2:$A$26,"&lt;"&amp;(A4+7))</f>
         <v>1</v>
       </c>
       <c r="H4" s="2" t="n">
-        <f aca="false">SUMIFS(Interviews!$I$2:$I$25,Interviews!$A$2:$A$25,"&gt;="&amp;A4,Interviews!$A$2:$A$25,"&lt;"&amp;(A4+7))</f>
+        <f aca="false">SUMIFS(Interviews!$I$2:$I$26,Interviews!$A$2:$A$26,"&gt;="&amp;A4,Interviews!$A$2:$A$26,"&lt;"&amp;(A4+7))</f>
         <v>0</v>
       </c>
       <c r="I4" s="11" t="n">
@@ -8221,7 +8663,7 @@
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A4,Interviews!$A$2:$A$25,"&lt;"&amp;(A4+7),Interviews!$B$2:$B$25,"Yulia")</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A4,Interviews!$A$2:$A$26,"&lt;"&amp;(A4+7),Interviews!$B$2:$B$26,"Yulia")</f>
         <v>1</v>
       </c>
       <c r="L4" s="2" t="n">
@@ -8250,11 +8692,11 @@
         <v>36</v>
       </c>
       <c r="G5" s="2" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A5,Interviews!$A$2:$A$25,"&lt;"&amp;(A5+7))</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A5,Interviews!$A$2:$A$26,"&lt;"&amp;(A5+7))</f>
         <v>3</v>
       </c>
       <c r="H5" s="2" t="n">
-        <f aca="false">SUMIFS(Interviews!$I$2:$I$25,Interviews!$A$2:$A$25,"&gt;="&amp;A5,Interviews!$A$2:$A$25,"&lt;"&amp;(A5+7))</f>
+        <f aca="false">SUMIFS(Interviews!$I$2:$I$26,Interviews!$A$2:$A$26,"&gt;="&amp;A5,Interviews!$A$2:$A$26,"&lt;"&amp;(A5+7))</f>
         <v>0</v>
       </c>
       <c r="I5" s="11" t="n">
@@ -8263,7 +8705,7 @@
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A5,Interviews!$A$2:$A$25,"&lt;"&amp;(A5+7),Interviews!$B$2:$B$25,"Yulia")</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A5,Interviews!$A$2:$A$26,"&lt;"&amp;(A5+7),Interviews!$B$2:$B$26,"Yulia")</f>
         <v>3</v>
       </c>
       <c r="L5" s="2" t="n">
@@ -8292,11 +8734,11 @@
         <v>42</v>
       </c>
       <c r="G6" s="2" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A6,Interviews!$A$2:$A$25,"&lt;"&amp;(A6+7))</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A6,Interviews!$A$2:$A$26,"&lt;"&amp;(A6+7))</f>
         <v>1</v>
       </c>
       <c r="H6" s="2" t="n">
-        <f aca="false">SUMIFS(Interviews!$I$2:$I$25,Interviews!$A$2:$A$25,"&gt;="&amp;A6,Interviews!$A$2:$A$25,"&lt;"&amp;(A6+7))</f>
+        <f aca="false">SUMIFS(Interviews!$I$2:$I$26,Interviews!$A$2:$A$26,"&gt;="&amp;A6,Interviews!$A$2:$A$26,"&lt;"&amp;(A6+7))</f>
         <v>0</v>
       </c>
       <c r="I6" s="11" t="n">
@@ -8305,7 +8747,7 @@
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A6,Interviews!$A$2:$A$25,"&lt;"&amp;(A6+7),Interviews!$B$2:$B$25,"Yulia")</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A6,Interviews!$A$2:$A$26,"&lt;"&amp;(A6+7),Interviews!$B$2:$B$26,"Yulia")</f>
         <v>1</v>
       </c>
       <c r="L6" s="2" t="n">
@@ -8334,11 +8776,11 @@
         <v>34</v>
       </c>
       <c r="G7" s="2" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A7,Interviews!$A$2:$A$25,"&lt;"&amp;(A7+7))</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A7,Interviews!$A$2:$A$26,"&lt;"&amp;(A7+7))</f>
         <v>4</v>
       </c>
       <c r="H7" s="2" t="n">
-        <f aca="false">SUMIFS(Interviews!$I$2:$I$25,Interviews!$A$2:$A$25,"&gt;="&amp;A7,Interviews!$A$2:$A$25,"&lt;"&amp;(A7+7))</f>
+        <f aca="false">SUMIFS(Interviews!$I$2:$I$26,Interviews!$A$2:$A$26,"&gt;="&amp;A7,Interviews!$A$2:$A$26,"&lt;"&amp;(A7+7))</f>
         <v>0</v>
       </c>
       <c r="I7" s="11" t="n">
@@ -8350,7 +8792,7 @@
         <v>0.0725806451612903</v>
       </c>
       <c r="K7" s="2" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A7,Interviews!$A$2:$A$25,"&lt;"&amp;(A7+7),Interviews!$B$2:$B$25,"Yulia")</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A7,Interviews!$A$2:$A$26,"&lt;"&amp;(A7+7),Interviews!$B$2:$B$26,"Yulia")</f>
         <v>4</v>
       </c>
       <c r="L7" s="2" t="n">
@@ -8379,11 +8821,11 @@
         <v>39</v>
       </c>
       <c r="G8" s="2" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A8,Interviews!$A$2:$A$25,"&lt;"&amp;(A8+7))</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A8,Interviews!$A$2:$A$26,"&lt;"&amp;(A8+7))</f>
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <f aca="false">SUMIFS(Interviews!$I$2:$I$25,Interviews!$A$2:$A$25,"&gt;="&amp;A8,Interviews!$A$2:$A$25,"&lt;"&amp;(A8+7))</f>
+        <f aca="false">SUMIFS(Interviews!$I$2:$I$26,Interviews!$A$2:$A$26,"&gt;="&amp;A8,Interviews!$A$2:$A$26,"&lt;"&amp;(A8+7))</f>
         <v>0</v>
       </c>
       <c r="I8" s="11" t="n">
@@ -8395,7 +8837,7 @@
         <v>0.0529801324503311</v>
       </c>
       <c r="K8" s="2" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A8,Interviews!$A$2:$A$25,"&lt;"&amp;(A8+7),Interviews!$B$2:$B$25,"Yulia")</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A8,Interviews!$A$2:$A$26,"&lt;"&amp;(A8+7),Interviews!$B$2:$B$26,"Yulia")</f>
         <v>0</v>
       </c>
       <c r="L8" s="2" t="n">
@@ -8411,7 +8853,7 @@
         <v>4</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" s="16" t="n">
         <v>4</v>
@@ -8421,31 +8863,31 @@
       </c>
       <c r="F9" s="2" t="n">
         <f aca="false">SUM(B9:E9)</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G9" s="2" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A9,Interviews!$A$2:$A$25,"&lt;"&amp;(A9+7))</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A9,Interviews!$A$2:$A$26,"&lt;"&amp;(A9+7))</f>
+        <v>3</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <f aca="false">SUMIFS(Interviews!$I$2:$I$26,Interviews!$A$2:$A$26,"&gt;="&amp;A9,Interviews!$A$2:$A$26,"&lt;"&amp;(A9+7))</f>
         <v>2</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <f aca="false">SUMIFS(Interviews!$I$2:$I$25,Interviews!$A$2:$A$25,"&gt;="&amp;A9,Interviews!$A$2:$A$25,"&lt;"&amp;(A9+7))</f>
-        <v>1</v>
       </c>
       <c r="I9" s="11" t="n">
         <f aca="false">IFERROR(G9/F9,0)</f>
-        <v>0.0512820512820513</v>
+        <v>0.075</v>
       </c>
       <c r="J9" s="11" t="n">
         <f aca="false">IFERROR(SUM(G6:G9)/SUM(F6:F9),0)</f>
-        <v>0.0454545454545455</v>
+        <v>0.0516129032258065</v>
       </c>
       <c r="K9" s="2" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A9,Interviews!$A$2:$A$25,"&lt;"&amp;(A9+7),Interviews!$B$2:$B$25,"Yulia")</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A9,Interviews!$A$2:$A$26,"&lt;"&amp;(A9+7),Interviews!$B$2:$B$26,"Yulia")</f>
         <v>1</v>
       </c>
       <c r="L9" s="2" t="n">
         <f aca="false">G9-K9</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8469,11 +8911,11 @@
         <v>42</v>
       </c>
       <c r="G10" s="2" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A10,Interviews!$A$2:$A$25,"&lt;"&amp;(A10+7))</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A10,Interviews!$A$2:$A$26,"&lt;"&amp;(A10+7))</f>
         <v>1</v>
       </c>
       <c r="H10" s="2" t="n">
-        <f aca="false">SUMIFS(Interviews!$I$2:$I$25,Interviews!$A$2:$A$25,"&gt;="&amp;A10,Interviews!$A$2:$A$25,"&lt;"&amp;(A10+7))</f>
+        <f aca="false">SUMIFS(Interviews!$I$2:$I$26,Interviews!$A$2:$A$26,"&gt;="&amp;A10,Interviews!$A$2:$A$26,"&lt;"&amp;(A10+7))</f>
         <v>0</v>
       </c>
       <c r="I10" s="11" t="n">
@@ -8482,10 +8924,10 @@
       </c>
       <c r="J10" s="11" t="n">
         <f aca="false">IFERROR(SUM(G7:G10)/SUM(F7:F10),0)</f>
-        <v>0.0454545454545455</v>
+        <v>0.0516129032258065</v>
       </c>
       <c r="K10" s="2" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A10,Interviews!$A$2:$A$25,"&lt;"&amp;(A10+7),Interviews!$B$2:$B$25,"Yulia")</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A10,Interviews!$A$2:$A$26,"&lt;"&amp;(A10+7),Interviews!$B$2:$B$26,"Yulia")</f>
         <v>0</v>
       </c>
       <c r="L10" s="2" t="n">
@@ -8514,11 +8956,11 @@
         <v>44</v>
       </c>
       <c r="G11" s="2" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A11,Interviews!$A$2:$A$25,"&lt;"&amp;(A11+7))</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A11,Interviews!$A$2:$A$26,"&lt;"&amp;(A11+7))</f>
         <v>2</v>
       </c>
       <c r="H11" s="2" t="n">
-        <f aca="false">SUMIFS(Interviews!$I$2:$I$25,Interviews!$A$2:$A$25,"&gt;="&amp;A11,Interviews!$A$2:$A$25,"&lt;"&amp;(A11+7))</f>
+        <f aca="false">SUMIFS(Interviews!$I$2:$I$26,Interviews!$A$2:$A$26,"&gt;="&amp;A11,Interviews!$A$2:$A$26,"&lt;"&amp;(A11+7))</f>
         <v>0</v>
       </c>
       <c r="I11" s="11" t="n">
@@ -8527,10 +8969,10 @@
       </c>
       <c r="J11" s="11" t="n">
         <f aca="false">IFERROR(SUM(G8:G11)/SUM(F8:F11),0)</f>
-        <v>0.0304878048780488</v>
+        <v>0.0363636363636364</v>
       </c>
       <c r="K11" s="2" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A11,Interviews!$A$2:$A$25,"&lt;"&amp;(A11+7),Interviews!$B$2:$B$25,"Yulia")</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A11,Interviews!$A$2:$A$26,"&lt;"&amp;(A11+7),Interviews!$B$2:$B$26,"Yulia")</f>
         <v>2</v>
       </c>
       <c r="L11" s="2" t="n">
@@ -8559,11 +9001,11 @@
         <v>41</v>
       </c>
       <c r="G12" s="2" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A12,Interviews!$A$2:$A$25,"&lt;"&amp;(A12+7))</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A12,Interviews!$A$2:$A$26,"&lt;"&amp;(A12+7))</f>
         <v>2</v>
       </c>
       <c r="H12" s="2" t="n">
-        <f aca="false">SUMIFS(Interviews!$I$2:$I$25,Interviews!$A$2:$A$25,"&gt;="&amp;A12,Interviews!$A$2:$A$25,"&lt;"&amp;(A12+7))</f>
+        <f aca="false">SUMIFS(Interviews!$I$2:$I$26,Interviews!$A$2:$A$26,"&gt;="&amp;A12,Interviews!$A$2:$A$26,"&lt;"&amp;(A12+7))</f>
         <v>0</v>
       </c>
       <c r="I12" s="11" t="n">
@@ -8572,10 +9014,10 @@
       </c>
       <c r="J12" s="11" t="n">
         <f aca="false">IFERROR(SUM(G9:G12)/SUM(F9:F12),0)</f>
-        <v>0.0421686746987952</v>
+        <v>0.0479041916167665</v>
       </c>
       <c r="K12" s="2" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A12,Interviews!$A$2:$A$25,"&lt;"&amp;(A12+7),Interviews!$B$2:$B$25,"Yulia")</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A12,Interviews!$A$2:$A$26,"&lt;"&amp;(A12+7),Interviews!$B$2:$B$26,"Yulia")</f>
         <v>2</v>
       </c>
       <c r="L12" s="2" t="n">
@@ -8604,11 +9046,11 @@
         <v>51</v>
       </c>
       <c r="G13" s="2" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A13,Interviews!$A$2:$A$25,"&lt;"&amp;(A13+7))</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A13,Interviews!$A$2:$A$26,"&lt;"&amp;(A13+7))</f>
         <v>5</v>
       </c>
       <c r="H13" s="2" t="n">
-        <f aca="false">SUMIFS(Interviews!$I$2:$I$25,Interviews!$A$2:$A$25,"&gt;="&amp;A13,Interviews!$A$2:$A$25,"&lt;"&amp;(A13+7))</f>
+        <f aca="false">SUMIFS(Interviews!$I$2:$I$26,Interviews!$A$2:$A$26,"&gt;="&amp;A13,Interviews!$A$2:$A$26,"&lt;"&amp;(A13+7))</f>
         <v>0</v>
       </c>
       <c r="I13" s="11" t="n">
@@ -8620,7 +9062,7 @@
         <v>0.0561797752808989</v>
       </c>
       <c r="K13" s="2" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A13,Interviews!$A$2:$A$25,"&lt;"&amp;(A13+7),Interviews!$B$2:$B$25,"Yulia")</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A13,Interviews!$A$2:$A$26,"&lt;"&amp;(A13+7),Interviews!$B$2:$B$26,"Yulia")</f>
         <v>4</v>
       </c>
       <c r="L13" s="2" t="n">
@@ -8649,11 +9091,11 @@
         <v>49</v>
       </c>
       <c r="G14" s="2" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A14,Interviews!$A$2:$A$25,"&lt;"&amp;(A14+7))</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A14,Interviews!$A$2:$A$26,"&lt;"&amp;(A14+7))</f>
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <f aca="false">SUMIFS(Interviews!$I$2:$I$25,Interviews!$A$2:$A$25,"&gt;="&amp;A14,Interviews!$A$2:$A$25,"&lt;"&amp;(A14+7))</f>
+        <f aca="false">SUMIFS(Interviews!$I$2:$I$26,Interviews!$A$2:$A$26,"&gt;="&amp;A14,Interviews!$A$2:$A$26,"&lt;"&amp;(A14+7))</f>
         <v>0</v>
       </c>
       <c r="I14" s="11" t="n">
@@ -8665,7 +9107,7 @@
         <v>0.0486486486486487</v>
       </c>
       <c r="K14" s="2" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A14,Interviews!$A$2:$A$25,"&lt;"&amp;(A14+7),Interviews!$B$2:$B$25,"Yulia")</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A14,Interviews!$A$2:$A$26,"&lt;"&amp;(A14+7),Interviews!$B$2:$B$26,"Yulia")</f>
         <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
@@ -8694,12 +9136,12 @@
         <v>42</v>
       </c>
       <c r="G15" s="2" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A15,Interviews!$A$2:$A$25,"&lt;"&amp;(A15+7))</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A15,Interviews!$A$2:$A$26,"&lt;"&amp;(A15+7))</f>
         <v>2</v>
       </c>
       <c r="H15" s="2" t="n">
-        <f aca="false">SUMIFS(Interviews!$I$2:$I$25,Interviews!$A$2:$A$25,"&gt;="&amp;A15,Interviews!$A$2:$A$25,"&lt;"&amp;(A15+7))</f>
-        <v>0</v>
+        <f aca="false">SUMIFS(Interviews!$I$2:$I$26,Interviews!$A$2:$A$26,"&gt;="&amp;A15,Interviews!$A$2:$A$26,"&lt;"&amp;(A15+7))</f>
+        <v>1</v>
       </c>
       <c r="I15" s="11" t="n">
         <f aca="false">IFERROR(G15/F15,0)</f>
@@ -8710,7 +9152,7 @@
         <v>0.0491803278688525</v>
       </c>
       <c r="K15" s="2" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A15,Interviews!$A$2:$A$25,"&lt;"&amp;(A15+7),Interviews!$B$2:$B$25,"Yulia")</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A15,Interviews!$A$2:$A$26,"&lt;"&amp;(A15+7),Interviews!$B$2:$B$26,"Yulia")</f>
         <v>1</v>
       </c>
       <c r="L15" s="2" t="n">
@@ -8739,11 +9181,11 @@
         <v>10</v>
       </c>
       <c r="G16" s="2" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A16,Interviews!$A$2:$A$25,"&lt;"&amp;(A16+7))</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A16,Interviews!$A$2:$A$26,"&lt;"&amp;(A16+7))</f>
         <v>1</v>
       </c>
       <c r="H16" s="2" t="n">
-        <f aca="false">SUMIFS(Interviews!$I$2:$I$25,Interviews!$A$2:$A$25,"&gt;="&amp;A16,Interviews!$A$2:$A$25,"&lt;"&amp;(A16+7))</f>
+        <f aca="false">SUMIFS(Interviews!$I$2:$I$26,Interviews!$A$2:$A$26,"&gt;="&amp;A16,Interviews!$A$2:$A$26,"&lt;"&amp;(A16+7))</f>
         <v>0</v>
       </c>
       <c r="I16" s="11" t="n">
@@ -8755,7 +9197,7 @@
         <v>0.0526315789473684</v>
       </c>
       <c r="K16" s="2" t="n">
-        <f aca="false">COUNTIFS(Interviews!$A$2:$A$25,"&gt;="&amp;A16,Interviews!$A$2:$A$25,"&lt;"&amp;(A16+7),Interviews!$B$2:$B$25,"Yulia")</f>
+        <f aca="false">COUNTIFS(Interviews!$A$2:$A$26,"&gt;="&amp;A16,Interviews!$A$2:$A$26,"&lt;"&amp;(A16+7),Interviews!$B$2:$B$26,"Yulia")</f>
         <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
@@ -8765,7 +9207,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="B17" s="19" t="n">
         <f aca="false">SUM(B4:B16)</f>
@@ -8773,7 +9215,7 @@
       </c>
       <c r="C17" s="19" t="n">
         <f aca="false">SUM(C4:C16)</f>
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D17" s="19" t="n">
         <f aca="false">SUM(D4:D16)</f>
@@ -8785,19 +9227,19 @@
       </c>
       <c r="F17" s="19" t="n">
         <f aca="false">SUM(F4:F16)</f>
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G17" s="19" t="n">
         <f aca="false">SUM(G4:G16)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H17" s="19" t="n">
         <f aca="false">SUM(H4:H16)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I17" s="22" t="n">
         <f aca="false">IFERROR(G17/F17,0)</f>
-        <v>0.0498960498960499</v>
+        <v>0.0518672199170125</v>
       </c>
       <c r="J17" s="20"/>
       <c r="K17" s="19" t="n">
@@ -8806,12 +9248,12 @@
       </c>
       <c r="L17" s="19" t="n">
         <f aca="false">SUM(L4:L16)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -8844,7 +9286,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -8875,99 +9317,386 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="15" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>222</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>46227</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <f aca="false">IF(A5="","",A5-F5)</f>
+        <v>12</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <f aca="false">IF(AND(A5&gt;=DATE(2026,8,1),A5&lt;=DATE(2026,10,20)),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="15" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>46269</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <f aca="false">IF(A6="","",A6-F6)</f>
+        <v>4</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <f aca="false">IF(AND(A6&gt;=DATE(2026,8,1),A6&lt;=DATE(2026,10,20)),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="15" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>46268</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <f aca="false">IF(A7="","",A7-F7)</f>
+        <v>15</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <f aca="false">IF(AND(A7&gt;=DATE(2026,8,1),A7&lt;=DATE(2026,10,20)),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="15" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <f aca="false">IF(A8="","",A8-F8)</f>
+        <v>1</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <f aca="false">IF(AND(A8&gt;=DATE(2026,8,1),A8&lt;=DATE(2026,10,20)),1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="15"/>
+      <c r="B9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>46211</v>
+      </c>
+      <c r="G9" s="2" t="str">
+        <f aca="false">IF(A9="","",A9-F9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="2" t="n">
+        <f aca="false">IF(AND(A9&gt;=DATE(2026,8,1),A9&lt;=DATE(2026,10,20)),1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="19" t="n">
+        <f aca="false">SUM(H5:H9)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="19" t="n">
+        <f aca="false">SUMPRODUCT((H5:H9=1)*(E5:E9="Nstya"))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="23" t="n">
+        <f aca="false">AVERAGE(G5:G9)</f>
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="120"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="26" t="s">
-        <v>207</v>
+      <c r="A1" s="27" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="27" t="s">
-        <v>208</v>
+      <c r="A2" s="28" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="27" t="s">
-        <v>209</v>
+      <c r="A3" s="28" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="27" t="s">
-        <v>210</v>
+      <c r="A4" s="28" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="27" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="27" t="s">
-        <v>212</v>
+      <c r="A5" s="28" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="28" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="27"/>
+      <c r="A7" s="28"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="26" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="27" t="s">
-        <v>214</v>
+      <c r="A8" s="27" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="28" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="27"/>
+      <c r="A10" s="28"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="26" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="27" t="s">
-        <v>216</v>
+      <c r="A11" s="27" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="28" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="27" t="s">
-        <v>217</v>
+      <c r="A13" s="28" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="27" t="s">
-        <v>218</v>
+      <c r="A14" s="28" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="27" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="27" t="s">
-        <v>220</v>
+      <c r="A15" s="28" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="28" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="27"/>
+      <c r="A17" s="28" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="27" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="27" t="s">
-        <v>222</v>
+      <c r="A18" s="28"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="28" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="28" t="s">
+        <v>245</v>
       </c>
     </row>
   </sheetData>
